--- a/セリフ編集/キャラタイプ別/標準×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×真面目.xlsx
@@ -438,7 +438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -496,22 +496,22 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.standard.hit[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.hit[1]</t>
+          <t xml:space="preserve">atk.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -521,29 +521,29 @@
       </c>
       <c r="F2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで倒れたら、迎えてくれた団体に顔向けできない。</t>
+          <t xml:space="preserve">絶対に…勝つ！</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.standard.hit[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.hit[2]</t>
+          <t xml:space="preserve">atk.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -553,29 +553,29 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立てる。証明の途中で、終われない。</t>
+          <t xml:space="preserve">ここで引くわけにはいかない！</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.standard.win[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.win[1]</t>
+          <t xml:space="preserve">atk.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -585,29 +585,29 @@
       </c>
       <c r="F4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切られてから、積み上げてきた。この一勝が、その証明。</t>
+          <t xml:space="preserve">全力で…いく！</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.standard.win[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.earnest[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.win[2]</t>
+          <t xml:space="preserve">atk.standard.earnest[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -617,1228 +617,4460 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれた団体に、恥はかかせない。だから、あそこには勝つ。</t>
+          <t xml:space="preserve">諦めない…！</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.lose[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.lose[1]</t>
+          <t xml:space="preserve">bigmove.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けました。すみませんでした。</t>
+          <t xml:space="preserve">絶対に…ここで決める！</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.lose[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.lose[2]</t>
+          <t xml:space="preserve">bigmove.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言い出したのは私です。……この結果は、全部私の責任です。</t>
+          <t xml:space="preserve">全力で…いきます！</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.lose[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.lose[3]</t>
+          <t xml:space="preserve">bigmove.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです。……それ以上に、申し訳ないです。</t>
+          <t xml:space="preserve">負けたくない…だから…！</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.petition[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.petition[1]</t>
+          <t xml:space="preserve">climax.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、迷惑をかけるのは分かってます。それでも、あの人とやらせてください。</t>
+          <t xml:space="preserve">（ここまで来た…あとは、出し切るだけ）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.petition[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.petition[2]</t>
+          <t xml:space="preserve">climax.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">半端な気持ちじゃありません。……あの人と、闘わせてください。</t>
+          <t xml:space="preserve">（全部…全部出し切る）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.petition[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.petition[3]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いします。この一戦だけは、逃げたくないんです。</t>
+          <t xml:space="preserve">ぐっ…！ まだ…立てる…！</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.sendoff[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.sendoff[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。……この決断、無駄にしません。</t>
+          <t xml:space="preserve">くぅ…っ！ 効いた…けど…！</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.sendoff[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.sendoff[2]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">許してもらった分は、結果で返します。行ってきます。</t>
+          <t xml:space="preserve">はぁ…はぁ…負けるもんか…！</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.sendoff[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.earnest.hit[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.sendoff[3]</t>
+          <t xml:space="preserve">standard.earnest.hit[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。……背負って、行ってきます。</t>
+          <t xml:space="preserve">ここで倒れたら、迎えてくれた団体に顔向けできない。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.earnest.hit[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.win[1]</t>
+          <t xml:space="preserve">standard.earnest.hit[2]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……社長、ありがとうございました。</t>
+          <t xml:space="preserve">まだ立てる。証明の途中で、終われない。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.earnest.win[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.win[2]</t>
+          <t xml:space="preserve">standard.earnest.win[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">約束は守れました。……ほっとしています。</t>
+          <t xml:space="preserve">切られてから、積み上げてきた。この一勝が、その証明。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.win[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.earnest.win[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.win[3]</t>
+          <t xml:space="preserve">standard.earnest.win[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。……送り出してもらった甲斐が、ありました。</t>
+          <t xml:space="preserve">拾ってくれた団体に、恥はかかせない。だから、あそこには勝つ。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest._accept[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest._accept[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだ以上、真正面から受けます。</t>
+          <t xml:space="preserve">間に合わない…！</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest._accept[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest._accept[2]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その覚悟、無駄にはしません。必ず応えます。</t>
+          <t xml:space="preserve">動けない…！</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest._accept[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest._accept[3]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げません。全部、受け止めます。</t>
+          <t xml:space="preserve">……守れなかった</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.draw[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.draw[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着をつけられなかった。……それが一番悔しい。</t>
+          <t xml:space="preserve">そうはさせない！</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.draw[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.draw[2]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わりにはできません。もう一度。</t>
+          <t xml:space="preserve">まだ諦めてない！</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.draw[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.draw[3]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">宙ぶらりんのままです。……気持ちが収まりません。</t>
+          <t xml:space="preserve">絶対渡さない！</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.lose[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.lose[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けておいて、この結果です。……情けない。</t>
+          <t xml:space="preserve">一緒に…！</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.lose[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.lose[2]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが上でした。全部、わたしの責任です。</t>
+          <t xml:space="preserve">タイミング合わせて！</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.lose[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.lose[3]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。……この悔しさは、抱えていきます。</t>
+          <t xml:space="preserve">二人で決めよう！</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.win[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.win[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けた以上、負けられませんでした。</t>
+          <t xml:space="preserve">お疲れ様、あとは任せて！</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.win[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.win[2]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……あの目は、忘れません。</t>
+          <t xml:space="preserve">よく守った、交代だ！</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.win[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_earnest.win[3]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……重い一戦でした。</t>
+          <t xml:space="preserve">ここからは私が背負う！</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.earnest.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本当は、一つにまとまりたかった。でも……私たちには、譲れないものがある。</t>
+          <t xml:space="preserve">{partner}…私の力不足だ。あなたを勝たせてあげられなかった…</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.earnest.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘ですよね……？　まだ、教わりたいことがたくさんあったのに……。</t>
+          <t xml:space="preserve">ここまで繋いでくれたのに…{partner}、ごめん。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.earnest.standard[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard[2]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私たちは、どうしたらいいんでしょうか。</t>
+          <t xml:space="preserve">{partner}、あなたを信じてよかった。この勝ち、二人のものだよ。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.earnest.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……私、どうしてもあの人たちの側にいたいんです。</t>
+          <t xml:space="preserve">{partner}が繋いでくれたから…最後まで諦めずに済んだ。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.earnest.standard[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.lose[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard[2]</t>
+          <t xml:space="preserve">standard_earnest.lose[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じていたのに、気づいたら距離ができてて……。</t>
+          <t xml:space="preserve">……負けました。すみませんでした。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.earnest.standard[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.lose[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard[1]</t>
+          <t xml:space="preserve">standard_earnest.lose[2]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。私たちのこと、もっと見ていただきたいんです。</t>
+          <t xml:space="preserve">言い出したのは私です。……この結果は、全部私の責任です。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.earnest.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.lose[3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.high[1]</t>
+          <t xml:space="preserve">standard_earnest.lose[3]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てて、よかった。みんなのおかげです</t>
+          <t xml:space="preserve">悔しいです。……それ以上に、申し訳ないです。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.earnest.standard.high[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.petition[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.high[2]</t>
+          <t xml:space="preserve">standard_earnest.petition[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの組、今日のために積み上げてきたんです</t>
+          <t xml:space="preserve">社長、迷惑をかけるのは分かってます。それでも、あの人とやらせてください。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.earnest.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.petition[2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.high[1]</t>
+          <t xml:space="preserve">standard_earnest.petition[2]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございました。次の人に繋ぎます</t>
+          <t xml:space="preserve">半端な気持ちじゃありません。……あの人と、闘わせてください。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.earnest.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.petition[3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.high[1]</t>
+          <t xml:space="preserve">standard_earnest.petition[3]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">派閥同士の決着、今夜つけさせていただきます</t>
+          <t xml:space="preserve">お願いします。この一戦だけは、逃げたくないんです。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.earnest.standard.high[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.sendoff[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.high[2]</t>
+          <t xml:space="preserve">standard_earnest.sendoff[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの組のみんなのためにも、今日は引きません</t>
+          <t xml:space="preserve">ありがとうございます。……この決断、無駄にしません。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.earnest.standard.mid[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.sendoff[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.mid[1]</t>
+          <t xml:space="preserve">standard_earnest.sendoff[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この夜が、わたしたちの答えになります</t>
+          <t xml:space="preserve">許してもらった分は、結果で返します。行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.earnest.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.sendoff[3]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.standard.high[1]</t>
+          <t xml:space="preserve">standard_earnest.sendoff[3]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかりました。受けて立たせていただきます</t>
+          <t xml:space="preserve">ありがとうございます。……背負って、行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.earnest.standard.high[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.win[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.win[1]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。……社長、ありがとうございました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.win[2]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.win[2]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">約束は守れました。……ほっとしています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_earnest.win[3]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.win[3]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てました。……送り出してもらった甲斐が、ありました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest._accept[1]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest._accept[1]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしを選んだ以上、真正面から受けます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest._accept[2]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest._accept[2]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">その覚悟、無駄にはしません。必ず応えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest._accept[3]</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest._accept[3]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">逃げません。全部、受け止めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.draw[1]</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.draw[1]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着をつけられなかった。……それが一番悔しい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.draw[2]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.draw[2]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これで終わりにはできません。もう一度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.draw[3]</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.draw[3]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">宙ぶらりんのままです。……気持ちが収まりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.lose[1]</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.lose[1]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受けておいて、この結果です。……情けない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.lose[2]</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.lose[2]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あなたが上でした。全部、わたしの責任です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.lose[3]</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.lose[3]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けました。……この悔しさは、抱えていきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.win[1]</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.win[1]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受けた以上、負けられませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.win[2]</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.win[2]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。……あの目は、忘れません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_earnest.win[3]</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_earnest.win[3]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。……重い一戦でした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、お願いがあります。私たちのメンバーのこと、気にかけてもらえないでしょうか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、お願いがあります。次の興行のメイン、私たちにやらせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、図々しいお願いですが、私たちのメンバーの待遇を見直していただけませんか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、私たちの貢献、もし届いていれば、一言いただけませんか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます。私たちも、もっと社長に応えたいと思います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。私が言いたかったのは、まさにそういうことかもしれません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本当にありがとうございます。必ず応えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、承知しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。気にかけてくださって。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、本当にありがとうございます。応えなければ、と気が引き締まります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…承知しました。図々しいお願いだったかもしれません、すみませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。お金じゃない部分で、気にかけていただけるなんて。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本当にありがとうございます。これからも、見ていてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…承知しました。図々しいことを申しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。形は違っても、気にかけていただけるのは嬉しいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…申し訳ありません。輪の外にいる子の気持ち、見えてませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。いただいた寛容に甘え過ぎないようにします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…申し訳ありません、配慮が足りませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…申し訳ありません。リングの外にまで持ち込むのは、確かに行きすぎでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…申し訳ありません。立場のある身で、お恥ずかしい限りです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。お見逃しいただいたぶん、行動で返します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。私の不在の分、メンバーが寂しい思いをしないように。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…ご厚意に、甘えさせてもらいます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。チームで支えてもらえるなら、私も持ち直せます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…申し訳ありません。私がしっかり見ていれば、防げたはずです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。穏便に収まるよう努めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。私の力不足を、社長に補っていただいて。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…申し訳ありません。改めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（唇を結んだまま、頷くだけだった）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。気をつけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…申し訳ありません。私の判断が、行きすぎていました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。責任は私が持ちます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。私が見落としていた負担を、社長に拾っていただいて。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.standard</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.attack.standard</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">けじめを、つけさせてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.standard</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.defend.standard</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">逃げるつもりはありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr" s="2">
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんなで一つのはずだったのに……こんなの、違う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本当に変わってほしい。だから、声を上げなきゃ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずっと、こうして話せたらって思ってたんです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの頃のこと、お互いに少しずつ……手放せたらいいですね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これ以上は、話し合いでは済まない。わかってるはず。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.earnest.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめんなさい。私、勝てなかった……</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.earnest.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……みんな、ごめん。次は、絶対に</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.earnest.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（声にならない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.earnest.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……うっ……ごめん……みんな……</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……あなたの組のやり方が、間違ってたって、これで証明された</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私、勝ちました。みんなのために</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.earnest.high[3]</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[3]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう、うちの子たちを傷つけないでください</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.earnest.low[1]</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.low[1]</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝てた。みんなのおかげです</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとう……みんな、見ててくれて</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あなたたちのやり方は……許せない。今日で決着をつける</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私、あなたを倒さないと、後ろのみんなに顔向けできない</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.earnest.high[3]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[3]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うしろにいる子たちのために、今日は逃げない</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.earnest.low[1]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.low[1]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">リングの上で、答えを出しましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は、絶対に引きません</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.earnest.mid[2]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.mid[2]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あなたの組の流儀には、もう従えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……分かりました。今日、あなたの全てを受け止めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私のうしろの子たちも、もう泣かせない。受けて立ちます</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.earnest.low[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.low[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受けます。リングで、お会いしましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">逃げません。今日は、決着をつけましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめんなさい、みんな。わたしの責任です</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今夜は、わたしたちが弱かった。立て直します</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝てて、よかった。みんなのおかげです</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うちの組、今日のために積み上げてきたんです</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ごめんなさい、次に繋いでください</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ありがとうございました。次の人に繋ぎます</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お願いします</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で行きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">派閥同士の決着、今夜つけさせていただきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うちの組のみんなのためにも、今日は引きません</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.mid[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この夜が、わたしたちの答えになります</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">earnest.standard.high[2]</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr" s="3">
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わかりました。受けて立たせていただきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うちの組も、引きません</t>
         </is>
       </c>
     </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.earnest.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……あなたの方が、上でした。素直に認めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.earnest.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あとは、お任せします。立派に、組を率いてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.earnest.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……託します</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.earnest.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けました。次は、支える側に回ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ありがとうございました。この座、必ず守ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">重い……でも、引き受けます</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……失礼を承知で言います。私が、上に立ちます</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あなたを尊敬しています。だからこそ、今日、超える</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.earnest.high[3]</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[3]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">後ろの子たちに、もう待ってと言えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[1]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……来なさい。それが、あなたの覚悟なら</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest.high[2]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わかった。今日は、本気で迎え撃つ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H43"/>
+  <autoFilter ref="A1:H144"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×真面目.xlsx
@@ -438,7 +438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H530"/>
+  <dimension ref="A1:H532"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えて見せます。よろしくお願いしますね！</t>
+          <t xml:space="preserve">期待に応えてみせます。よろしくお願いしますね！</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待ってた甲斐がありました。この団体で輝いて見せますね！</t>
+          <t xml:space="preserve">待ってた甲斐がありました。この団体で輝いてみせますね！</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだ以上、真正面から受けます。</t>
+          <t xml:space="preserve">私を選んだ以上、真正面から受けます。</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが上でした。全部、わたしの責任です。</t>
+          <t xml:space="preserve">あなたが上でした。全部、私の責任です。</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい、みんな。わたしの責任です</t>
+          <t xml:space="preserve">……ごめんなさい、みんな。私の責任です</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今夜は、わたしたちが弱かった。立て直します</t>
+          <t xml:space="preserve">今夜は、私たちが弱かった。立て直します</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この夜が、わたしたちの答えになります</t>
+          <t xml:space="preserve">この夜が、私たちの答えになります</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">autumnWarChampion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9262,14 +9262,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合のためにずっと準備してきた。報われました</t>
+          <t xml:space="preserve">仲間の思いを背負って戦い、優勝で応えられて光栄です。</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">bestMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9294,14 +9294,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い全部出し切れた。これがプロレスだと思います</t>
+          <t xml:space="preserve">あの試合のためにずっと準備してきた。報われました</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[1]</t>
+          <t xml:space="preserve">bestMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9326,14 +9326,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンとして恥じない試合を、毎回見せる。それが自分との約束</t>
+          <t xml:space="preserve">お互い全部出し切れた。これがプロレスだと思います</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[2]</t>
+          <t xml:space="preserve">champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9358,14 +9358,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつひとつの防衛戦に全力を注ぐ。それだけ</t>
+          <t xml:space="preserve">チャンピオンとして恥じない試合を、毎回見せる。それが自分との約束</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.earnest[1]</t>
+          <t xml:space="preserve">champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9390,14 +9390,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩たちへ。リングの上に答えがある。苦しくても立ち続けてほしい</t>
+          <t xml:space="preserve">ひとつひとつの防衛戦に全力を注ぐ。それだけ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.earnest[2]</t>
+          <t xml:space="preserve">hallOfFame.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9422,14 +9422,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この業界に全てを捧げた。…後輩たちがもっと高い場所に行ってくれたら、それが一番嬉しい</t>
+          <t xml:space="preserve">後輩たちへ。リングの上に答えがある。苦しくても立ち続けてほしい</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.earnest[1]</t>
+          <t xml:space="preserve">hallOfFame.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9454,14 +9454,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日の練習が無駄じゃなかった。でもまだ先がある</t>
+          <t xml:space="preserve">この業界に全てを捧げた。…後輩たちがもっと高い場所に行ってくれたら、それが一番嬉しい</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.earnest[2]</t>
+          <t xml:space="preserve">mvp.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9486,14 +9486,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞は自分だけのものじゃない。一緒に戦ってくれたみんなのもの</t>
+          <t xml:space="preserve">毎日の練習が無駄じゃなかった。でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.earnest[1]</t>
+          <t xml:space="preserve">mvp.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9518,14 +9518,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習してきてよかった。…もっと強くなります</t>
+          <t xml:space="preserve">この賞は自分だけのものじゃない。一緒に戦ってくれたみんなのもの</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9535,12 +9535,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">rookie.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9550,14 +9550,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームで試合をさせていただけること、感謝いたします</t>
+          <t xml:space="preserve">練習してきてよかった。…もっと強くなります</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">springTagChampion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9582,14 +9582,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全身全霊で、臨ませていただきます</t>
+          <t xml:space="preserve">支えてくれた相棒と応援してくださった皆さんに、心から感謝します。</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.earnest[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[3]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9614,14 +9614,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この機会、絶対に無駄にしません</t>
+          <t xml:space="preserve">ドームで試合をさせていただけること、感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9646,14 +9646,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様に応えられる試合ができたか、反省と感謝でいっぱいです</t>
+          <t xml:space="preserve">全身全霊で、臨ませていただきます</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9678,14 +9678,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございました</t>
+          <t xml:space="preserve">この機会、絶対に無駄にしません</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.earnest[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[3]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9710,14 +9710,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと良い試合を、必ずお見せします</t>
+          <t xml:space="preserve">満員のお客様に応えられる試合ができたか、反省と感謝でいっぱいです</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9727,29 +9727,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが大事だと思ってます。コツコツやっていきます</t>
+          <t xml:space="preserve">社長、本当にありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.earnest[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9759,29 +9759,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習って楽しい。もっとやりたいです</t>
+          <t xml:space="preserve">次はもっと良い試合を、必ずお見せします</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.earnest[1]</t>
+          <t xml:space="preserve">N1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9806,14 +9806,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と練習してると自分も頑張ろうって思えるんです</t>
+          <t xml:space="preserve">積み重ねが大事だと思ってます。コツコツやっていきます</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.earnest[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.earnest[2]</t>
+          <t xml:space="preserve">N1.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9838,14 +9838,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体で一緒にやれる仲間がいて、幸せです</t>
+          <t xml:space="preserve">練習って楽しい。もっとやりたいです</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.earnest[1]</t>
+          <t xml:space="preserve">N2.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9870,14 +9870,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…体が追いつかなくて。少し休めば大丈夫です</t>
+          <t xml:space="preserve">あの人と練習してると自分も頑張ろうって思えるんです</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.earnest[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.earnest[2]</t>
+          <t xml:space="preserve">N2.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9902,14 +9902,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">立て直してみせます</t>
+          <t xml:space="preserve">この団体で一緒にやれる仲間がいて、幸せです</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.earnest[1]</t>
+          <t xml:space="preserve">N3.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9934,14 +9934,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなに応援してもらえるって、本当に力になりますね</t>
+          <t xml:space="preserve">すみません…体が追いつかなくて。少し休めば大丈夫です</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.earnest[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.earnest[2]</t>
+          <t xml:space="preserve">N3.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9966,14 +9966,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの声が原動力です</t>
+          <t xml:space="preserve">立て直してみせます</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.earnest[1]</t>
+          <t xml:space="preserve">N4.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9998,14 +9998,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切りたいわけじゃない。ただ……</t>
+          <t xml:space="preserve">みんなに応援してもらえるって、本当に力になりますね</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.earnest[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.earnest[2]</t>
+          <t xml:space="preserve">N4.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -10030,14 +10030,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが好きだから、だから辛いんです</t>
+          <t xml:space="preserve">ファンの声が原動力です</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.earnest[1]</t>
+          <t xml:space="preserve">N5_low.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -10062,14 +10062,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習しても練習しても、何かが足りない気がして…</t>
+          <t xml:space="preserve">裏切りたいわけじゃない。ただ……</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.earnest[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.earnest[2]</t>
+          <t xml:space="preserve">N5_low.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10094,14 +10094,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいたい気持ちは変わらないんですけど……</t>
+          <t xml:space="preserve">ここが好きだから、だから辛いんです</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10126,14 +10126,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなのおかげです。もっと恩返しがしたい</t>
+          <t xml:space="preserve">練習しても練習しても、何かが足りない気がして…</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10158,14 +10158,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと結果を出せばいいだけの話、だよね</t>
+          <t xml:space="preserve">…ここにいたい気持ちは変わらないんですけど……</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.earnest[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.standard.earnest[2]</t>
+          <t xml:space="preserve">breakthrough.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10190,14 +10190,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…自分の力不足かな</t>
+          <t xml:space="preserve">…みんなのおかげです。もっと恩返しがしたい</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">G1.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10222,14 +10222,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの子が評価されるのは正しいと思う。思うんだけど</t>
+          <t xml:space="preserve">…もっと結果を出せばいいだけの話、だよね</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">G1.voice.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10254,14 +10254,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…実力が足りないから？ それとも…</t>
+          <t xml:space="preserve">…自分の力不足かな</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.earnest[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.standard.earnest[2]</t>
+          <t xml:space="preserve">G2.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10286,14 +10286,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し、待てばいいのかな</t>
+          <t xml:space="preserve">…あの子が評価されるのは正しいと思う。思うんだけど</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">G3.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10318,14 +10318,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる。いつでも</t>
+          <t xml:space="preserve">…実力が足りないから？ それとも…</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">G3.voice.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10350,14 +10350,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっとみんなと話した方がいいのかな</t>
+          <t xml:space="preserve">…もう少し、待てばいいのかな</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.standard.earnest[1]</t>
+          <t xml:space="preserve">G4.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10382,14 +10382,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name2}のために、あたしはここで頑張るから</t>
+          <t xml:space="preserve">…準備はできてる。いつでも</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.earnest[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.standard.earnest[2]</t>
+          <t xml:space="preserve">R2.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10414,14 +10414,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。ずっと支えてくれて</t>
+          <t xml:space="preserve">…もっとみんなと話した方がいいのかな</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">R3.modal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10446,14 +10446,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…努力は裏切らない。…{name2}、ありがとう</t>
+          <t xml:space="preserve">{name2}のために、私はここで頑張るから</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">R3.modal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10478,14 +10478,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人にはまだ勝てない。でも、だからこそ</t>
+          <t xml:space="preserve">…ありがとう。ずっと支えてくれて</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.earnest[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.standard.earnest[2]</t>
+          <t xml:space="preserve">R4.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10510,14 +10510,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと練習する。絶対に</t>
+          <t xml:space="preserve">…努力は裏切らない。…{name2}、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.standard.earnest[1]</t>
+          <t xml:space="preserve">R5.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10542,14 +10542,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなの想いを背負って戦えて光栄です</t>
+          <t xml:space="preserve">…あの人にはまだ勝てない。でも、だからこそ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10559,29 +10559,29 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.standard.earnest[1]</t>
+          <t xml:space="preserve">R5.voice.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……私の頑張りは、これくらいなんですね</t>
+          <t xml:space="preserve">…もっと練習する。絶対に</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10591,29 +10591,29 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.standard.earnest[1]</t>
+          <t xml:space="preserve">warVictory.voice.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの…気持ちは嬉しいんですが…</t>
+          <t xml:space="preserve">…みんなの想いを背負って戦えて光栄です</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.earnest[1]</t>
+          <t xml:space="preserve">bonus_insult.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10638,14 +10638,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます！次の試合、絶対頑張ります！</t>
+          <t xml:space="preserve">……私の頑張りは、これくらいなんですね</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.earnest[2]</t>
+          <t xml:space="preserve">bonus_repeat.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10670,14 +10670,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつもありがとうございます</t>
+          <t xml:space="preserve">あの…気持ちは嬉しいんですが…</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.earnest[1]</t>
+          <t xml:space="preserve">bonus.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10702,14 +10702,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった！思い切り練習できる！</t>
+          <t xml:space="preserve">ありがとうございます！次の試合、絶対頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.earnest[2]</t>
+          <t xml:space="preserve">bonus.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10734,14 +10734,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿の間に絶対レベルアップしてみせます！</t>
+          <t xml:space="preserve">…いつもありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.earnest[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.earnest[3]</t>
+          <t xml:space="preserve">camp.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10766,14 +10766,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで一緒に強くなれるなんて…最高です</t>
+          <t xml:space="preserve">やった！思い切り練習できる！</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.earnest[1]</t>
+          <t xml:space="preserve">camp.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10798,14 +10798,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたに言われると、本当に力が出ます！もっと頑張れます！</t>
+          <t xml:space="preserve">合宿の間に絶対レベルアップしてみせます！</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.earnest[2]</t>
+          <t xml:space="preserve">camp.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10830,14 +10830,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくれてたんですね…絶対に報いてみせます</t>
+          <t xml:space="preserve">みんなで一緒に強くなれるなんて…最高です</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.earnest[1]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10862,14 +10862,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみます！</t>
+          <t xml:space="preserve">あなたに言われると、本当に力が出ます！もっと頑張れます！</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.earnest[2]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10894,14 +10894,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その言葉、すごく嬉しかったです。頑張ります！</t>
+          <t xml:space="preserve">ずっと見てくれてたんですね…絶対に報いてみせます</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.earnest[1]</t>
+          <t xml:space="preserve">encourage.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10926,14 +10926,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしのやり方が、間違っていたということでしょうか</t>
+          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみます！</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.earnest[2]</t>
+          <t xml:space="preserve">encourage.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10958,14 +10958,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もっと、うまくやれたはずでした</t>
+          <t xml:space="preserve">その言葉、すごく嬉しかったです。頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.earnest[1]</t>
+          <t xml:space="preserve">faction_decree.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10990,14 +10990,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うわあ、緊張する…でも頑張ります！</t>
+          <t xml:space="preserve">私のやり方が、間違っていたということでしょうか</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.earnest[2]</t>
+          <t xml:space="preserve">faction_decree.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -11022,14 +11022,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の看板として恥ずかしくないようにします</t>
+          <t xml:space="preserve">……もっと、うまくやれたはずでした</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.earnest[1]</t>
+          <t xml:space="preserve">media.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -11054,14 +11054,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなお疲れ様でした！明日からまた頑張ります！</t>
+          <t xml:space="preserve">うわあ、緊張する…でも頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.earnest[2]</t>
+          <t xml:space="preserve">media.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11086,14 +11086,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こうしてみんなで集まれるのが嬉しいです</t>
+          <t xml:space="preserve">団体の看板として恥ずかしくないようにします</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.earnest[1]</t>
+          <t xml:space="preserve">party.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11118,14 +11118,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え…でも練習が…でも、ありがとうございます！</t>
+          <t xml:space="preserve">みんなお疲れ様でした！明日からまた頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.earnest[2]</t>
+          <t xml:space="preserve">party.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11150,14 +11150,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そんなに気にかけてもらえるとは。ありがとうございます</t>
+          <t xml:space="preserve">こうしてみんなで集まれるのが嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.earnest[1]</t>
+          <t xml:space="preserve">refresh_leave.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11182,14 +11182,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに気にかけてもらえるなんて…必ず期待に応えます</t>
+          <t xml:space="preserve">え…でも練習が…でも、ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.earnest[2]</t>
+          <t xml:space="preserve">refresh_leave.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11214,14 +11214,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私のためにここまで…早く戻って、結果でお返しします</t>
+          <t xml:space="preserve">…そんなに気にかけてもらえるとは。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.earnest[1]</t>
+          <t xml:space="preserve">special_treatment.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11246,14 +11246,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">専属の先生がつくんですか…！もっと上手くなれます！</t>
+          <t xml:space="preserve">こんなに気にかけてもらえるなんて…必ず期待に応えます</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.earnest[2]</t>
+          <t xml:space="preserve">special_treatment.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11278,14 +11278,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をいただけて…全力で応えます</t>
+          <t xml:space="preserve">…私のためにここまで…早く戻って、結果でお返しします</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11295,12 +11295,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.earnest[1]</t>
+          <t xml:space="preserve">trainer.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11310,14 +11310,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビは緊張しますけど…精一杯やります！</t>
+          <t xml:space="preserve">専属の先生がつくんですか…！もっと上手くなれます！</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11327,12 +11327,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.earnest[1]</t>
+          <t xml:space="preserve">trainer.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11342,14 +11342,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらに義理があるので断りましたが…報告しておきます</t>
+          <t xml:space="preserve">こんな機会をいただけて…全力で応えます</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.earnest[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.earnest[2]</t>
+          <t xml:space="preserve">E1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11374,14 +11374,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと離れたくない気持ちはあるけど…正直、迷ってます</t>
+          <t xml:space="preserve">テレビは緊張しますけど…精一杯やります！</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.earnest[1]</t>
+          <t xml:space="preserve">E6.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11406,14 +11406,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…今日はどうしても体が動かなくて…</t>
+          <t xml:space="preserve">こちらに義理があるので断りましたが…報告しておきます</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.earnest[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.earnest[2]</t>
+          <t xml:space="preserve">E6.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11438,14 +11438,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習に集中できなくて…申し訳ありません</t>
+          <t xml:space="preserve">みんなと離れたくない気持ちはあるけど…正直、迷ってます</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.standard.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11470,14 +11470,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「自分、このままでいいんですかね…」と後輩に弱音を吐いている）</t>
+          <t xml:space="preserve">すみません…今日はどうしても体が動かなくて…</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.standard.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11502,14 +11502,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「自分は本当にここで必要とされているのか」と率直な投稿）</t>
+          <t xml:space="preserve">練習に集中できなくて…申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.earnest[1]</t>
+          <t xml:space="preserve">S_grumble.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11534,14 +11534,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備してきました…チャンスをください</t>
+          <t xml:space="preserve">（「自分、このままでいいんですかね…」と後輩に弱音を吐いている）</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.earnest[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.earnest[2]</t>
+          <t xml:space="preserve">S_sns.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11566,14 +11566,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチに挑ませてください！</t>
+          <t xml:space="preserve">（SNSに「自分は本当にここで必要とされているのか」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.earnest[1]</t>
+          <t xml:space="preserve">S1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11598,14 +11598,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの相手を越えてこそ、次のステージに行ける。組んでください</t>
+          <t xml:space="preserve">ずっと準備してきました…チャンスをください</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.earnest[1]</t>
+          <t xml:space="preserve">S1.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11630,14 +11630,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">迷惑をかけてしまって申し訳ないんですが…少し休ませてもらえますか</t>
+          <t xml:space="preserve">タイトルマッチに挑ませてください！</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.earnest[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.earnest[2]</t>
+          <t xml:space="preserve">S2.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11662,14 +11662,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チームに迷惑はかけたくないんですが…体が限界で…</t>
+          <t xml:space="preserve">あの相手を越えてこそ、次のステージに行ける。組んでください</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.earnest[1]</t>
+          <t xml:space="preserve">S3.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11694,14 +11694,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと我慢してきました。でも、このままでは…</t>
+          <t xml:space="preserve">迷惑をかけてしまって申し訳ないんですが…少し休ませてもらえますか</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.earnest[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.earnest[2]</t>
+          <t xml:space="preserve">S3.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11726,14 +11726,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の目標を達成できる環境が必要です。考え直してもらえませんか</t>
+          <t xml:space="preserve">チームに迷惑はかけたくないんですが…体が限界で…</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.standard.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11758,14 +11758,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何か言いたげに口を開きかけ、止める）</t>
+          <t xml:space="preserve">…ずっと我慢してきました。でも、このままでは…</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11790,14 +11790,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいんです。特訓を許可してください！</t>
+          <t xml:space="preserve">私の目標を達成できる環境が必要です。考え直してもらえませんか</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.earnest[1]</t>
+          <t xml:space="preserve">S4_silent.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11822,14 +11822,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が培ってきたものを、後輩に伝えたいと思って…</t>
+          <t xml:space="preserve">…………（何か言いたげに口を開きかけ、止める）</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.earnest[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.earnest[2]</t>
+          <t xml:space="preserve">S5.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11854,14 +11854,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩に何かを伝えたいんです。指導の機会をもらえますか</t>
+          <t xml:space="preserve">もっと強くなりたいんです。特訓を許可してください！</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.standard.earnest[1]</t>
+          <t xml:space="preserve">S6.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11886,14 +11886,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お任せください…精一杯務めます</t>
+          <t xml:space="preserve">私が培ってきたものを、後輩に伝えたいと思って…</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11903,12 +11903,12 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.standard.earnest[1]</t>
+          <t xml:space="preserve">S6.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11918,14 +11918,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご指名、ありがとうございます。精一杯やります</t>
+          <t xml:space="preserve">後輩に何かを伝えたいんです。指導の機会をもらえますか</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.earnest[1]</t>
+          <t xml:space="preserve">E1.accept.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11950,14 +11950,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません…もっと注意するべきでした。早く復帰できるよう頑張ります</t>
+          <t xml:space="preserve">お任せください…精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.earnest[1]</t>
+          <t xml:space="preserve">E1.recommend.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11982,14 +11982,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足を引っ張る人間とは一緒にやれない</t>
+          <t xml:space="preserve">ご指名、ありがとうございます。精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.earnest[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.earnest[2]</t>
+          <t xml:space="preserve">B1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -12014,14 +12014,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは団体のためにならない。何とかしてほしい</t>
+          <t xml:space="preserve">すみません…もっと注意するべきでした。早く復帰できるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter1.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -12046,14 +12046,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体には迷惑をかけたくないけど…あの人とは無理です</t>
+          <t xml:space="preserve">手を抜く人と同じリングには立てない</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.earnest[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.earnest[2]</t>
+          <t xml:space="preserve">B2_fighter1.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -12078,14 +12078,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私のやり方に文句があるなら、はっきり言えばいい</t>
+          <t xml:space="preserve">このままでは団体のためにならない。何とかしてほしい</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -12110,14 +12110,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドさんのイメージを大切に。しっかり務めます</t>
+          <t xml:space="preserve">団体には迷惑をかけたくないけど…あの人とは無理です</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -12142,14 +12142,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM出演、しっかり準備します。恥ずかしくない姿を</t>
+          <t xml:space="preserve">私のやり方に文句があるなら、はっきり言えばいい</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.earnest[1]</t>
+          <t xml:space="preserve">B4_brand.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -12174,14 +12174,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆さん一人ひとりに、誠実に向き合います</t>
+          <t xml:space="preserve">ブランドさんのイメージを大切に。しっかり務めます</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.earnest[1]</t>
+          <t xml:space="preserve">B4_cm.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12206,14 +12206,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習して、ちゃんと歩けるよう準備します</t>
+          <t xml:space="preserve">CM出演、しっかり準備します。恥ずかしくない姿を</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.earnest[1]</t>
+          <t xml:space="preserve">B4_fan.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12238,14 +12238,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり準備して臨みます。でも…少し恥ずかしいですね</t>
+          <t xml:space="preserve">ファンの皆さん一人ひとりに、誠実に向き合います</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.earnest[1]</t>
+          <t xml:space="preserve">B4_fashion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12270,14 +12270,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うまく喋れるか不安ですが…精一杯やります</t>
+          <t xml:space="preserve">練習して、ちゃんと歩けるよう準備します</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.earnest[1]</t>
+          <t xml:space="preserve">B4_gravure.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12302,14 +12302,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私なんかでいいんですか？ …精一杯頑張ります！</t>
+          <t xml:space="preserve">しっかり準備して臨みます。でも…少し恥ずかしいですね</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12319,29 +12319,29 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">B4_variety.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道にコツコツ…それが私のやり方です。信じてもらえますか？</t>
+          <t xml:space="preserve">うまく喋れるか不安ですが…精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12351,29 +12351,29 @@
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">B4.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰よりも練習します。見ていてください</t>
+          <t xml:space="preserve">私でいいんですか？ …精一杯やらせていただきます！</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="12">
@@ -12398,14 +12398,14 @@
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくださって、ありがとうございます！ 精一杯頑張ります！</t>
+          <t xml:space="preserve">地道にコツコツ…それが私のやり方です。信じてもらえますか？</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="12">
@@ -12430,14 +12430,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道にコツコツ…努力で応えます</t>
+          <t xml:space="preserve">誰よりも練習します。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.earnest[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[3]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12462,14 +12462,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれる方々のためにも、頑張ります</t>
+          <t xml:space="preserve">選んでくださって、ありがとうございます！ 精一杯頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12479,12 +12479,12 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12494,14 +12494,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…毎日練習して、絶対に期待に応えます！</t>
+          <t xml:space="preserve">地道にコツコツ…努力で応えます</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12526,14 +12526,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この恩は忘れません。ずっとこの団体で戦います</t>
+          <t xml:space="preserve">応援してくれる方々のためにも、頑張ります</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="12">
@@ -12558,14 +12558,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日コツコツ、頑張ります！見ていてください！</t>
+          <t xml:space="preserve">ありがとうございます…毎日練習して、絶対に期待に応えます！</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="12">
@@ -12590,14 +12590,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体のために…全てを捧げます</t>
+          <t xml:space="preserve">この恩は忘れません。ずっとこの団体で戦います</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="12">
@@ -12622,14 +12622,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、すみません…</t>
+          <t xml:space="preserve">毎日コツコツ、頑張ります！見ていてください！</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="12">
@@ -12654,14 +12654,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず万全の状態で戻ってきます</t>
+          <t xml:space="preserve">この団体のために…全てを捧げます</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.earnest[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[3]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12686,14 +12686,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれるみんなに、申し訳ない…</t>
+          <t xml:space="preserve">ご期待に応えられず、すみません…</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12703,12 +12703,12 @@
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12718,14 +12718,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はつきました。……私の中だけ、まだです</t>
+          <t xml:space="preserve">必ず万全の状態で戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12735,12 +12735,12 @@
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12750,14 +12750,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った人間が引きずるのは、変な話ですね</t>
+          <t xml:space="preserve">応援してくれるみんなに、申し訳ない…</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12782,14 +12782,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの負けを、まだ一度も納得できていません</t>
+          <t xml:space="preserve">決着はつきました。……私の中だけ、まだです</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.earnest[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12814,14 +12814,14 @@
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったと言われるたび、足元が抜けるんです</t>
+          <t xml:space="preserve">勝った人間が引きずるのは、変な話ですね</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12846,14 +12846,14 @@
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道にコツコツ…それが私のやり方です。信じてもらえますか？</t>
+          <t xml:space="preserve">あの負けを、まだ一度も納得できていません</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.earnest[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12878,14 +12878,14 @@
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰よりも練習します。見ていてください</t>
+          <t xml:space="preserve">終わったと言われるたび、足元が抜けるんです</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.earnest[1]</t>
+          <t xml:space="preserve">draftInterest.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12910,14 +12910,14 @@
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくださって、ありがとうございます！ 精一杯頑張ります！</t>
+          <t xml:space="preserve">地道にコツコツ…それが私のやり方です。信じてもらえますか？</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.earnest[2]</t>
+          <t xml:space="preserve">draftInterest.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12942,14 +12942,14 @@
       </c>
       <c r="F390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道にコツコツ…努力で応えます</t>
+          <t xml:space="preserve">誰よりも練習します。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.earnest[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.earnest[3]</t>
+          <t xml:space="preserve">draftJoin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12974,14 +12974,14 @@
       </c>
       <c r="F391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれる方々のためにも、頑張ります</t>
+          <t xml:space="preserve">選んでくださって、ありがとうございます！ 精一杯頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -13006,14 +13006,14 @@
       </c>
       <c r="F392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度チャンスをもらえた。無駄にしません</t>
+          <t xml:space="preserve">地道にコツコツ…努力で応えます</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.earnest[2]</t>
+          <t xml:space="preserve">draftJoin.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -13038,14 +13038,14 @@
       </c>
       <c r="F393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれた恩は、練習の量でお返しします</t>
+          <t xml:space="preserve">応援してくれる方々のためにも、頑張ります</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.earnest[1]</t>
+          <t xml:space="preserve">faGreeting.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -13070,14 +13070,14 @@
       </c>
       <c r="F394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…毎日練習して、絶対に期待に応えます！</t>
+          <t xml:space="preserve">もう一度チャンスをもらえた。無駄にしません</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.earnest[2]</t>
+          <t xml:space="preserve">faGreeting.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -13102,14 +13102,14 @@
       </c>
       <c r="F395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この恩は忘れません。ずっとこの団体で戦います</t>
+          <t xml:space="preserve">声をかけてくれた恩には、積み上げた練習で応えます</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.earnest[1]</t>
+          <t xml:space="preserve">faSigning.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -13134,14 +13134,14 @@
       </c>
       <c r="F396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日コツコツ、頑張ります！見ていてください！</t>
+          <t xml:space="preserve">ありがとうございます…毎日練習して、絶対に期待に応えます！</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.earnest[2]</t>
+          <t xml:space="preserve">faSigning.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -13166,14 +13166,14 @@
       </c>
       <c r="F397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体のために…全てを捧げます</t>
+          <t xml:space="preserve">この恩は忘れません。ずっとこの団体で戦います</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.standard.earnest[1]</t>
+          <t xml:space="preserve">faWelcome.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -13198,14 +13198,14 @@
       </c>
       <c r="F398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が素直に動きます。やった分だけ返ってきます</t>
+          <t xml:space="preserve">毎日コツコツ、頑張ります！見ていてください！</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.standard.earnest[1]</t>
+          <t xml:space="preserve">faWelcome.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -13230,14 +13230,14 @@
       </c>
       <c r="F399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">動きが同じところで止まる。私の集中が足りないのかな</t>
+          <t xml:space="preserve">この団体のために…全てを捧げます</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.standard.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -13262,14 +13262,14 @@
       </c>
       <c r="F400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じだけやってるのに、身についてる感じがしません</t>
+          <t xml:space="preserve">体が素直に動きます。やった分だけ返ってきます</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -13294,14 +13294,14 @@
       </c>
       <c r="F401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、すみません…</t>
+          <t xml:space="preserve">動きが同じところで止まる。私の集中が足りないのかな</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.earnest[2]</t>
+          <t xml:space="preserve">heatSelf.warm.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -13326,14 +13326,14 @@
       </c>
       <c r="F402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず万全の状態で戻ってきます</t>
+          <t xml:space="preserve">同じだけやってるのに、身についてる感じがしません</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.earnest[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="D403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.earnest[3]</t>
+          <t xml:space="preserve">injury.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -13358,14 +13358,14 @@
       </c>
       <c r="F403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれるみんなに、申し訳ない…</t>
+          <t xml:space="preserve">ご期待に応えられず、すみません…</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="D404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.earnest[1]</t>
+          <t xml:space="preserve">injury.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -13390,14 +13390,14 @@
       </c>
       <c r="F404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれた皆様に、顔向けできません…でも、次で頑張ります</t>
+          <t xml:space="preserve">必ず万全の状態で戻ってきます</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.earnest[2]</t>
+          <t xml:space="preserve">injury.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13422,14 +13422,14 @@
       </c>
       <c r="F405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、どこに行っても忘れません</t>
+          <t xml:space="preserve">応援してくれるみんなに、申し訳ない…</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.earnest[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.earnest[3]</t>
+          <t xml:space="preserve">release.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13454,14 +13454,14 @@
       </c>
       <c r="F406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">結果を残せなくて、すみません。必ず、どこかで</t>
+          <t xml:space="preserve">応援してくれた皆様に、顔向けできません…でも、次で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.earnest[1]</t>
+          <t xml:space="preserve">release.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13486,14 +13486,14 @@
       </c>
       <c r="F407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い期間ですが、精一杯やらせていただきます！</t>
+          <t xml:space="preserve">ここでの学び、どこに行っても忘れません</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.earnest[2]</t>
+          <t xml:space="preserve">release.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13518,14 +13518,14 @@
       </c>
       <c r="F408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限られた時間でも成長したい。よろしくお願いします</t>
+          <t xml:space="preserve">結果を残せなくて、すみません。必ず、どこかで</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.earnest[1]</t>
+          <t xml:space="preserve">rentalGreeting.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13550,14 +13550,14 @@
       </c>
       <c r="F409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ていてくれた人がいた。それだけで頑張れます</t>
+          <t xml:space="preserve">短い期間ですが、精一杯やらせていただきます！</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.earnest[2]</t>
+          <t xml:space="preserve">rentalGreeting.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13582,14 +13582,14 @@
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待してもらった分、毎日積み上げていきます</t>
+          <t xml:space="preserve">限られた時間でも成長したい。よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.earnest[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13614,14 +13614,14 @@
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。もっと練習して、必ずもう一度挑戦します</t>
+          <t xml:space="preserve">見ていてくれた人がいた。それだけで頑張れます</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.earnest[2]</t>
+          <t xml:space="preserve">scoutGreeting.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13646,14 +13646,14 @@
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…でもここで腐っちゃだめだ</t>
+          <t xml:space="preserve">期待してもらった分、毎日積み上げていきます</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.earnest[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13678,14 +13678,14 @@
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できた…！でも満足しない。もっと強くなります</t>
+          <t xml:space="preserve">…足りなかった。もっと練習して、必ずもう一度挑戦します</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.earnest[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13710,14 +13710,14 @@
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日々の積み重ねが結果に出てくれた</t>
+          <t xml:space="preserve">悔しい…でもここで腐っちゃだめだ</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.earnest[1]</t>
+          <t xml:space="preserve">titleDefense.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13742,14 +13742,14 @@
       </c>
       <c r="F415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…努力が足りなかったんだ。もう一度、一からやり直します</t>
+          <t xml:space="preserve">防衛できた…！でも満足しない。もっと強くなります</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="D416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.earnest[2]</t>
+          <t xml:space="preserve">titleDefense.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13774,14 +13774,14 @@
       </c>
       <c r="F416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを手放してしまった…でもここで終わりじゃない</t>
+          <t xml:space="preserve">日々の積み重ねが結果に出てくれた</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="D417" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.earnest[1]</t>
+          <t xml:space="preserve">titleLoss.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13806,14 +13806,14 @@
       </c>
       <c r="F417" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねてきて…よかった。本当に、よかった…！</t>
+          <t xml:space="preserve">…努力が足りなかったんだ。もう一度、一からやり直します</t>
         </is>
       </c>
     </row>
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="D418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.earnest[2]</t>
+          <t xml:space="preserve">titleLoss.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13838,14 +13838,14 @@
       </c>
       <c r="F418" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">諦めなくてよかった…このベルト、努力の結晶です</t>
+          <t xml:space="preserve">ベルトを手放してしまった…でもここで終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13855,12 +13855,12 @@
       </c>
       <c r="C419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">titleWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13870,14 +13870,14 @@
       </c>
       <c r="F419" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれた皆様に、顔向けできません…でも、次で頑張ります</t>
+          <t xml:space="preserve">コツコツ積み重ねてきて…よかった。本当に、よかった…！</t>
         </is>
       </c>
     </row>
     <row r="420" ht="40" customHeight="1">
       <c r="A420" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13887,12 +13887,12 @@
       </c>
       <c r="C420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D420" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">titleWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13902,14 +13902,14 @@
       </c>
       <c r="F420" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、どこに行っても忘れません</t>
+          <t xml:space="preserve">諦めなくてよかった…このベルト、努力の結晶です</t>
         </is>
       </c>
     </row>
     <row r="421" ht="40" customHeight="1">
       <c r="A421" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.earnest[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="D421" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[3]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13934,14 +13934,14 @@
       </c>
       <c r="F421" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">結果を残せなくて、すみません。必ず、どこかで</t>
+          <t xml:space="preserve">応援してくれた皆様に、顔向けできません…でも、次で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="422" ht="40" customHeight="1">
       <c r="A422" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="C422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D422" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13966,14 +13966,14 @@
       </c>
       <c r="F422" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い期間ですが、精一杯やらせていただきます！</t>
+          <t xml:space="preserve">ここでの学び、どこに行っても忘れません</t>
         </is>
       </c>
     </row>
     <row r="423" ht="40" customHeight="1">
       <c r="A423" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
@@ -13983,12 +13983,12 @@
       </c>
       <c r="C423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D423" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="2">
@@ -13998,14 +13998,14 @@
       </c>
       <c r="F423" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限られた時間でも成長したい。よろしくお願いします</t>
+          <t xml:space="preserve">結果を残せなくて、すみません。必ず、どこかで</t>
         </is>
       </c>
     </row>
     <row r="424" ht="40" customHeight="1">
       <c r="A424" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="C424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D424" t="inlineStr" s="12">
@@ -14030,14 +14030,14 @@
       </c>
       <c r="F424" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…足りなかった。もっと練習して、必ずもう一度挑戦します</t>
+          <t xml:space="preserve">短い期間ですが、精一杯やらせていただきます！</t>
         </is>
       </c>
     </row>
     <row r="425" ht="40" customHeight="1">
       <c r="A425" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="C425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D425" t="inlineStr" s="12">
@@ -14062,14 +14062,14 @@
       </c>
       <c r="F425" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…でもここで腐っちゃだめだ</t>
+          <t xml:space="preserve">限られた時間でも成長したい。よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="426" ht="40" customHeight="1">
       <c r="A426" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="C426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D426" t="inlineStr" s="12">
@@ -14094,14 +14094,14 @@
       </c>
       <c r="F426" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できた…！でも満足しない。もっと強くなります</t>
+          <t xml:space="preserve">…足りなかった。もっと練習して、必ずもう一度挑戦します</t>
         </is>
       </c>
     </row>
     <row r="427" ht="40" customHeight="1">
       <c r="A427" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="C427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D427" t="inlineStr" s="12">
@@ -14126,14 +14126,14 @@
       </c>
       <c r="F427" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日々の積み重ねが結果に出てくれた</t>
+          <t xml:space="preserve">悔しい…でもここで腐っちゃだめだ</t>
         </is>
       </c>
     </row>
     <row r="428" ht="40" customHeight="1">
       <c r="A428" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="C428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D428" t="inlineStr" s="12">
@@ -14158,14 +14158,14 @@
       </c>
       <c r="F428" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…努力が足りなかったんだ。もう一度、一からやり直します</t>
+          <t xml:space="preserve">防衛できた…！でも満足しない。もっと強くなります</t>
         </is>
       </c>
     </row>
     <row r="429" ht="40" customHeight="1">
       <c r="A429" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="C429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D429" t="inlineStr" s="12">
@@ -14190,14 +14190,14 @@
       </c>
       <c r="F429" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを手放してしまった…でもここで終わりじゃない</t>
+          <t xml:space="preserve">日々の積み重ねが結果に出てくれた</t>
         </is>
       </c>
     </row>
     <row r="430" ht="40" customHeight="1">
       <c r="A430" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="C430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D430" t="inlineStr" s="12">
@@ -14222,14 +14222,14 @@
       </c>
       <c r="F430" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねてきて…よかった。本当に、よかった…！</t>
+          <t xml:space="preserve">…努力が足りなかったんだ。もう一度、一からやり直します</t>
         </is>
       </c>
     </row>
     <row r="431" ht="40" customHeight="1">
       <c r="A431" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D431" t="inlineStr" s="12">
@@ -14254,14 +14254,14 @@
       </c>
       <c r="F431" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">諦めなくてよかった…このベルト、努力の結晶です</t>
+          <t xml:space="preserve">ベルトを手放してしまった…でもここで終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="432" ht="40" customHeight="1">
       <c r="A432" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
@@ -14271,29 +14271,29 @@
       </c>
       <c r="C432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D432" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.standard[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F432" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この関係…修復できる自信がない…</t>
+          <t xml:space="preserve">コツコツ積み重ねてきて…よかった。本当に、よかった…！</t>
         </is>
       </c>
     </row>
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.standard[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -14303,29 +14303,29 @@
       </c>
       <c r="C433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.standard[2]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F433" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこで間違えたんだろう…</t>
+          <t xml:space="preserve">諦めなくてよかった…このベルト、努力の結晶です</t>
         </is>
       </c>
     </row>
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="D434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.standard[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="2">
@@ -14350,14 +14350,14 @@
       </c>
       <c r="F434" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この距離…自分の何がいけなかったんだろう</t>
+          <t xml:space="preserve">この関係…修復できる自信がない…</t>
         </is>
       </c>
     </row>
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="D435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.standard[2]</t>
+          <t xml:space="preserve">bond_39_down.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E435" t="inlineStr" s="2">
@@ -14382,14 +14382,14 @@
       </c>
       <c r="F435" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度、分かり合えるように努力しなきゃ</t>
+          <t xml:space="preserve">どこで間違えたんだろう…</t>
         </is>
       </c>
     </row>
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="D436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.standard[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E436" t="inlineStr" s="2">
@@ -14414,14 +14414,14 @@
       </c>
       <c r="F436" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に練習してて楽しいんです。もっと強くなれる気がして</t>
+          <t xml:space="preserve">この距離…自分の何がいけなかったんだろう</t>
         </is>
       </c>
     </row>
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="D437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.standard[2]</t>
+          <t xml:space="preserve">bond_59_down.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="2">
@@ -14446,14 +14446,14 @@
       </c>
       <c r="F437" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">背中を見てると、自分も頑張ろうって思える</t>
+          <t xml:space="preserve">もう一度、分かり合えるように努力しなきゃ</t>
         </is>
       </c>
     </row>
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="D438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.standard[1]</t>
+          <t xml:space="preserve">bond_60_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="2">
@@ -14478,14 +14478,14 @@
       </c>
       <c r="F438" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に頂点を目指したい。二人ならきっと行ける</t>
+          <t xml:space="preserve">一緒に練習してて楽しいんです。もっと強くなれる気がして</t>
         </is>
       </c>
     </row>
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="D439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.standard[2]</t>
+          <t xml:space="preserve">bond_60_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E439" t="inlineStr" s="2">
@@ -14510,14 +14510,14 @@
       </c>
       <c r="F439" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のパートナー。この出会いに感謝してます</t>
+          <t xml:space="preserve">背中を見てると、自分も頑張ろうって思える</t>
         </is>
       </c>
     </row>
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="D440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.standard[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="2">
@@ -14542,14 +14542,14 @@
       </c>
       <c r="F440" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係も変わった。前に進もう</t>
+          <t xml:space="preserve">一緒に頂点を目指したい。二人ならきっと行ける</t>
         </is>
       </c>
     </row>
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="D441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.standard[2]</t>
+          <t xml:space="preserve">bond_80_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="2">
@@ -14574,14 +14574,14 @@
       </c>
       <c r="F441" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁から学んだことは多い。次の目標を見つけなきゃ</t>
+          <t xml:space="preserve">最高のパートナー。この出会いに感謝してます</t>
         </is>
       </c>
     </row>
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="D442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.standard[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="2">
@@ -14606,14 +14606,14 @@
       </c>
       <c r="F442" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ライバルとして意識し始めている自分がいる</t>
+          <t xml:space="preserve">関係も変わった。前に進もう</t>
         </is>
       </c>
     </row>
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="D443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.standard[2]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E443" t="inlineStr" s="2">
@@ -14638,14 +14638,14 @@
       </c>
       <c r="F443" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えることが、今の一番の目標だ</t>
+          <t xml:space="preserve">あの因縁から学んだことは多い。次の目標を見つけなきゃ</t>
         </is>
       </c>
     </row>
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="D444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.standard[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E444" t="inlineStr" s="2">
@@ -14670,14 +14670,14 @@
       </c>
       <c r="F444" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この壁を超えない限り、自分の成長はない</t>
+          <t xml:space="preserve">ライバルとして意識し始めている自分がいる</t>
         </is>
       </c>
     </row>
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="D445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.standard[2]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E445" t="inlineStr" s="2">
@@ -14702,14 +14702,14 @@
       </c>
       <c r="F445" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最大の壁。だからこそ、越えなきゃいけない</t>
+          <t xml:space="preserve">超えることが、今の一番の目標だ</t>
         </is>
       </c>
     </row>
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="D446" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.standard[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E446" t="inlineStr" s="2">
@@ -14734,14 +14734,14 @@
       </c>
       <c r="F446" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この存在が自分を高めてくれる。これが宿命というものか</t>
+          <t xml:space="preserve">この壁を超えない限り、自分の成長はない</t>
         </is>
       </c>
     </row>
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="D447" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.standard[2]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E447" t="inlineStr" s="2">
@@ -14766,14 +14766,14 @@
       </c>
       <c r="F447" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戦えることに感謝してる。でも次は絶対に勝つ</t>
+          <t xml:space="preserve">最大の壁。だからこそ、越えなきゃいけない</t>
         </is>
       </c>
     </row>
     <row r="448" ht="40" customHeight="1">
       <c r="A448" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B448" t="inlineStr" s="2">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="D448" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.standard[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E448" t="inlineStr" s="2">
@@ -14798,14 +14798,14 @@
       </c>
       <c r="F448" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に貢献できるよう、これからも全力で努力します</t>
+          <t xml:space="preserve">この存在が自分を高めてくれる。これが宿命というものか</t>
         </is>
       </c>
     </row>
     <row r="449" ht="40" customHeight="1">
       <c r="A449" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="2">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="D449" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.standard[2]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E449" t="inlineStr" s="2">
@@ -14830,14 +14830,14 @@
       </c>
       <c r="F449" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめています</t>
+          <t xml:space="preserve">戦えることに感謝してる。でも次は絶対に勝つ</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40" customHeight="1">
       <c r="A450" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B450" t="inlineStr" s="2">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="D450" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.standard[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E450" t="inlineStr" s="2">
@@ -14862,14 +14862,14 @@
       </c>
       <c r="F450" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼してたのに…もうここでは頑張れないかもしれない</t>
+          <t xml:space="preserve">この団体に貢献できるよう、これからも全力で努力します</t>
         </is>
       </c>
     </row>
     <row r="451" ht="40" customHeight="1">
       <c r="A451" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B451" t="inlineStr" s="2">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="D451" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.standard[2]</t>
+          <t xml:space="preserve">trust_above_75.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E451" t="inlineStr" s="2">
@@ -14894,14 +14894,14 @@
       </c>
       <c r="F451" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分の全力を尽くしてきたつもりです。でも、もう…</t>
+          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめています</t>
         </is>
       </c>
     </row>
     <row r="452" ht="40" customHeight="1">
       <c r="A452" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B452" t="inlineStr" s="2">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="D452" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.standard[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E452" t="inlineStr" s="2">
@@ -14926,14 +14926,14 @@
       </c>
       <c r="F452" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の方針に…少し不安を感じています</t>
+          <t xml:space="preserve">信頼してたのに…もうここでは頑張れないかもしれない</t>
         </is>
       </c>
     </row>
     <row r="453" ht="40" customHeight="1">
       <c r="A453" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B453" t="inlineStr" s="2">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="D453" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.standard[2]</t>
+          <t xml:space="preserve">trust_below_20.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E453" t="inlineStr" s="2">
@@ -14958,14 +14958,14 @@
       </c>
       <c r="F453" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分の居場所がここにあるのか…考えてしまう</t>
+          <t xml:space="preserve">自分の全力を尽くしてきたつもりです。でも、もう…</t>
         </is>
       </c>
     </row>
     <row r="454" ht="40" customHeight="1">
       <c r="A454" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.standard[1]</t>
         </is>
       </c>
       <c r="B454" t="inlineStr" s="2">
@@ -14975,12 +14975,12 @@
       </c>
       <c r="C454" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D454" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.earnest[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.standard[1]</t>
         </is>
       </c>
       <c r="E454" t="inlineStr" s="2">
@@ -14990,14 +14990,14 @@
       </c>
       <c r="F454" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたが良い試合だった。この経験を糧にする</t>
+          <t xml:space="preserve">この団体の方針に…少し不安を感じています</t>
         </is>
       </c>
     </row>
     <row r="455" ht="40" customHeight="1">
       <c r="A455" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.standard[2]</t>
         </is>
       </c>
       <c r="B455" t="inlineStr" s="2">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="C455" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D455" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.earnest[2]</t>
+          <t xml:space="preserve">trust_below_35.earnest.standard[2]</t>
         </is>
       </c>
       <c r="E455" t="inlineStr" s="2">
@@ -15022,14 +15022,14 @@
       </c>
       <c r="F455" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人の強さを体感できた。次は必ず超える</t>
+          <t xml:space="preserve">自分の居場所がここにあるのか…考えてしまう</t>
         </is>
       </c>
     </row>
     <row r="456" ht="40" customHeight="1">
       <c r="A456" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B456" t="inlineStr" s="2">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="D456" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E456" t="inlineStr" s="2">
@@ -15054,14 +15054,14 @@
       </c>
       <c r="F456" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合で勝利。努力は裏切らないと証明できた</t>
+          <t xml:space="preserve">負けたが良い試合だった。この経験を糧にする</t>
         </is>
       </c>
     </row>
     <row r="457" ht="40" customHeight="1">
       <c r="A457" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B457" t="inlineStr" s="2">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="D457" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E457" t="inlineStr" s="2">
@@ -15086,14 +15086,14 @@
       </c>
       <c r="F457" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分の全てを出し切って勝てた。これ以上の幸せはない</t>
+          <t xml:space="preserve">あの人の強さを体感できた。次は必ず超える</t>
         </is>
       </c>
     </row>
     <row r="458" ht="40" customHeight="1">
       <c r="A458" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B458" t="inlineStr" s="2">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="D458" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E458" t="inlineStr" s="2">
@@ -15118,14 +15118,14 @@
       </c>
       <c r="F458" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…もっと練習しないと…</t>
+          <t xml:space="preserve">最高の試合で勝利。努力は裏切らないと証明できた</t>
         </is>
       </c>
     </row>
     <row r="459" ht="40" customHeight="1">
       <c r="A459" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B459" t="inlineStr" s="2">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="D459" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E459" t="inlineStr" s="2">
@@ -15150,14 +15150,14 @@
       </c>
       <c r="F459" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた原因を分析して、必ず次に活かす</t>
+          <t xml:space="preserve">自分の全てを出し切って勝てた。これ以上の幸せはない</t>
         </is>
       </c>
     </row>
     <row r="460" ht="40" customHeight="1">
       <c r="A460" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B460" t="inlineStr" s="2">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="D460" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-01.loss.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E460" t="inlineStr" s="2">
@@ -15182,14 +15182,14 @@
       </c>
       <c r="F460" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた。でもまだ課題はある。次に繋げよう</t>
+          <t xml:space="preserve">悔しい…もっと練習しないと…</t>
         </is>
       </c>
     </row>
     <row r="461" ht="40" customHeight="1">
       <c r="A461" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B461" t="inlineStr" s="2">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="D461" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-01.loss.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E461" t="inlineStr" s="2">
@@ -15214,14 +15214,14 @@
       </c>
       <c r="F461" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利を掴めたのは練習の成果。もっと上を目指す</t>
+          <t xml:space="preserve">負けた原因を分析して、必ず次に活かす</t>
         </is>
       </c>
     </row>
     <row r="462" ht="40" customHeight="1">
       <c r="A462" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B462" t="inlineStr" s="2">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="D462" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E462" t="inlineStr" s="2">
@@ -15246,14 +15246,14 @@
       </c>
       <c r="F462" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一つ一つの練習を大切に。基礎が全ての土台だ</t>
+          <t xml:space="preserve">勝てた。でもまだ課題はある。次に繋げよう</t>
         </is>
       </c>
     </row>
     <row r="463" ht="40" customHeight="1">
       <c r="A463" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B463" t="inlineStr" s="2">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="D463" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-01.win.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E463" t="inlineStr" s="2">
@@ -15278,14 +15278,14 @@
       </c>
       <c r="F463" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のメニューも全力でこなす。手は抜かない</t>
+          <t xml:space="preserve">勝利を掴めたのは練習の成果。もっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="464" ht="40" customHeight="1">
       <c r="A464" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B464" t="inlineStr" s="2">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="D464" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-02.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E464" t="inlineStr" s="2">
@@ -15310,14 +15310,14 @@
       </c>
       <c r="F464" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何か改善すべき点があるなら教えてほしい…</t>
+          <t xml:space="preserve">一つ一つの練習を大切に。基礎が全ての土台だ</t>
         </is>
       </c>
     </row>
     <row r="465" ht="40" customHeight="1">
       <c r="A465" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B465" t="inlineStr" s="2">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="D465" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-02.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E465" t="inlineStr" s="2">
@@ -15342,14 +15342,14 @@
       </c>
       <c r="F465" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼に応えるよう、より一層精進します</t>
+          <t xml:space="preserve">今日のメニューも全力でこなす。手は抜かない</t>
         </is>
       </c>
     </row>
     <row r="466" ht="40" customHeight="1">
       <c r="A466" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B466" t="inlineStr" s="2">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="D466" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E466" t="inlineStr" s="2">
@@ -15374,14 +15374,14 @@
       </c>
       <c r="F466" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切磋琢磨できる環境に感謝してる</t>
+          <t xml:space="preserve">何か改善すべき点があるなら教えてほしい…</t>
         </is>
       </c>
     </row>
     <row r="467" ht="40" customHeight="1">
       <c r="A467" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B467" t="inlineStr" s="2">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="D467" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E467" t="inlineStr" s="2">
@@ -15406,14 +15406,14 @@
       </c>
       <c r="F467" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">意識するからこそ成長できる</t>
+          <t xml:space="preserve">信頼に応えるよう、より一層精進します</t>
         </is>
       </c>
     </row>
     <row r="468" ht="40" customHeight="1">
       <c r="A468" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B468" t="inlineStr" s="2">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="D468" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-04.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E468" t="inlineStr" s="2">
@@ -15438,14 +15438,14 @@
       </c>
       <c r="F468" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場できなかった…次こそは選んでもらえるように頑張らないと</t>
+          <t xml:space="preserve">切磋琢磨できる環境に感謝してる</t>
         </is>
       </c>
     </row>
     <row r="469" ht="40" customHeight="1">
       <c r="A469" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B469" t="inlineStr" s="2">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="D469" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-05.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E469" t="inlineStr" s="2">
@@ -15470,14 +15470,14 @@
       </c>
       <c r="F469" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力不足なら練習で補う。必ず次は出場する</t>
+          <t xml:space="preserve">意識するからこそ成長できる</t>
         </is>
       </c>
     </row>
     <row r="470" ht="40" customHeight="1">
       <c r="A470" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B470" t="inlineStr" s="2">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="D470" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-06.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E470" t="inlineStr" s="2">
@@ -15502,14 +15502,14 @@
       </c>
       <c r="F470" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コンディションが良くない。焦らず回復に努めよう</t>
+          <t xml:space="preserve">出場できなかった…次こそは選んでもらえるように頑張らないと</t>
         </is>
       </c>
     </row>
     <row r="471" ht="40" customHeight="1">
       <c r="A471" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B471" t="inlineStr" s="2">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="D471" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-06.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E471" t="inlineStr" s="2">
@@ -15534,14 +15534,14 @@
       </c>
       <c r="F471" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗の原因を見つけなければ。何かが間違っているはずだ</t>
+          <t xml:space="preserve">実力不足なら練習で補う。必ず次は出場する</t>
         </is>
       </c>
     </row>
     <row r="472" ht="40" customHeight="1">
       <c r="A472" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B472" t="inlineStr" s="2">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="D472" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-07.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E472" t="inlineStr" s="2">
@@ -15566,14 +15566,14 @@
       </c>
       <c r="F472" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けが続いている。でも腐らない。必ず糸口はある</t>
+          <t xml:space="preserve">コンディションが良くない。焦らず回復に努めよう</t>
         </is>
       </c>
     </row>
     <row r="473" ht="40" customHeight="1">
       <c r="A473" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B473" t="inlineStr" s="2">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="D473" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-08.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E473" t="inlineStr" s="2">
@@ -15598,14 +15598,14 @@
       </c>
       <c r="F473" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝は努力の証。でも油断はしない。謙虚にいこう</t>
+          <t xml:space="preserve">連敗の原因を見つけなければ。何かが間違っているはずだ</t>
         </is>
       </c>
     </row>
     <row r="474" ht="40" customHeight="1">
       <c r="A474" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B474" t="inlineStr" s="2">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="D474" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-08.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E474" t="inlineStr" s="2">
@@ -15630,14 +15630,14 @@
       </c>
       <c r="F474" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リハビリに全力で取り組む。一日でも早く復帰する</t>
+          <t xml:space="preserve">負けが続いている。でも腐らない。必ず糸口はある</t>
         </is>
       </c>
     </row>
     <row r="475" ht="40" customHeight="1">
       <c r="A475" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B475" t="inlineStr" s="2">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="D475" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-09.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E475" t="inlineStr" s="2">
@@ -15662,14 +15662,14 @@
       </c>
       <c r="F475" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我の間もできることはある。頭を鍛える時間にする</t>
+          <t xml:space="preserve">連勝は努力の証。でも油断はしない。謙虚にいこう</t>
         </is>
       </c>
     </row>
     <row r="476" ht="40" customHeight="1">
       <c r="A476" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B476" t="inlineStr" s="2">
@@ -15679,12 +15679,12 @@
       </c>
       <c r="C476" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D476" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">GL-10.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E476" t="inlineStr" s="2">
@@ -15694,14 +15694,14 @@
       </c>
       <c r="F476" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調は終わったけど…あの期間で掴んだものがある</t>
+          <t xml:space="preserve">リハビリに全力で取り組む。一日でも早く復帰する</t>
         </is>
       </c>
     </row>
     <row r="477" ht="40" customHeight="1">
       <c r="A477" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B477" t="inlineStr" s="2">
@@ -15711,12 +15711,12 @@
       </c>
       <c r="C477" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D477" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">GL-10.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E477" t="inlineStr" s="2">
@@ -15726,14 +15726,14 @@
       </c>
       <c r="F477" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの好調は偶然じゃない。努力の結果だ。また必ず来る</t>
+          <t xml:space="preserve">怪我の間もできることはある。頭を鍛える時間にする</t>
         </is>
       </c>
     </row>
     <row r="478" ht="40" customHeight="1">
       <c r="A478" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B478" t="inlineStr" s="2">
@@ -15743,29 +15743,29 @@
       </c>
       <c r="C478" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D478" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E478" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F478" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでもらった。最後は、私が全部背負って立ちます</t>
+          <t xml:space="preserve">絶好調は終わったけど…あの期間で掴んだものがある</t>
         </is>
       </c>
     </row>
     <row r="479" ht="40" customHeight="1">
       <c r="A479" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B479" t="inlineStr" s="2">
@@ -15775,29 +15775,29 @@
       </c>
       <c r="C479" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D479" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E479" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F479" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界です。でも、託された役目を、途中で降りるわけにはいきません</t>
+          <t xml:space="preserve">あの好調は偶然じゃない。努力の結果だ。また必ず来る</t>
         </is>
       </c>
     </row>
     <row r="480" ht="40" customHeight="1">
       <c r="A480" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B480" t="inlineStr" s="2">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="D480" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[3]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E480" t="inlineStr" s="2">
@@ -15822,14 +15822,14 @@
       </c>
       <c r="F480" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけでも、この一戦だけは譲れません。全部、出し切ります</t>
+          <t xml:space="preserve">ここまで繋いでもらった。最後は、私が全部背負って立ちます</t>
         </is>
       </c>
     </row>
     <row r="481" ht="40" customHeight="1">
       <c r="A481" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B481" t="inlineStr" s="2">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="D481" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E481" t="inlineStr" s="2">
@@ -15854,14 +15854,14 @@
       </c>
       <c r="F481" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どんな相手でも、全力で。仲間に繋ぐ、それだけは絶対です</t>
+          <t xml:space="preserve">身体は限界です。でも、託された役目を、途中で降りるわけにはいきません</t>
         </is>
       </c>
     </row>
     <row r="482" ht="40" customHeight="1">
       <c r="A482" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B482" t="inlineStr" s="2">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="D482" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E482" t="inlineStr" s="2">
@@ -15886,14 +15886,14 @@
       </c>
       <c r="F482" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目の前の一戦から、正面で受けます。手を抜く理由がありません</t>
+          <t xml:space="preserve">傷だらけでも、この一戦だけは譲れません。全部、出し切ります</t>
         </is>
       </c>
     </row>
     <row r="483" ht="40" customHeight="1">
       <c r="A483" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B483" t="inlineStr" s="2">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="D483" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[3]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E483" t="inlineStr" s="2">
@@ -15918,14 +15918,14 @@
       </c>
       <c r="F483" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、確実に。託されたものを、途中で放り出せませんから</t>
+          <t xml:space="preserve">どんな相手でも、全力で。仲間に繋ぐ、それだけは絶対です</t>
         </is>
       </c>
     </row>
     <row r="484" ht="40" customHeight="1">
       <c r="A484" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B484" t="inlineStr" s="2">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="D484" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.earnest[1]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E484" t="inlineStr" s="2">
@@ -15950,14 +15950,14 @@
       </c>
       <c r="F484" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒しました。…はぁ、まだ退けません。繋ぐまで、ここは渡さない。次、来てください</t>
+          <t xml:space="preserve">目の前の一戦から、正面で受けます。手を抜く理由がありません</t>
         </is>
       </c>
     </row>
     <row r="485" ht="40" customHeight="1">
       <c r="A485" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B485" t="inlineStr" s="2">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="D485" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.earnest[2]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E485" t="inlineStr" s="2">
@@ -15982,14 +15982,14 @@
       </c>
       <c r="F485" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。託された役目、途中で放り出せない。次の相手、来てください</t>
+          <t xml:space="preserve">一戦ずつ、確実に。託されたものを、途中で放り出せませんから</t>
         </is>
       </c>
     </row>
     <row r="486" ht="40" customHeight="1">
       <c r="A486" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B486" t="inlineStr" s="2">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="D486" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.earnest[3]</t>
+          <t xml:space="preserve">survivor.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E486" t="inlineStr" s="2">
@@ -16014,14 +16014,14 @@
       </c>
       <c r="F486" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、受け止めました。…息は上がってますが、まだ役目の途中です。次、どうぞ</t>
+          <t xml:space="preserve">一人、倒しました。…はぁ、まだ退けません。繋ぐまで、ここは渡さない。次、来てください</t>
         </is>
       </c>
     </row>
     <row r="487" ht="40" customHeight="1">
       <c r="A487" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B487" t="inlineStr" s="2">
@@ -16031,12 +16031,12 @@
       </c>
       <c r="C487" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D487" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[1]</t>
+          <t xml:space="preserve">survivor.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E487" t="inlineStr" s="2">
@@ -16046,14 +16046,14 @@
       </c>
       <c r="F487" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">託された順番を守り抜けました。仲間と団体に、この勝利を返せてよかったです</t>
+          <t xml:space="preserve">まだ立ってます。託された役目、途中で放り出せない。次の相手、来てください</t>
         </is>
       </c>
     </row>
     <row r="488" ht="40" customHeight="1">
       <c r="A488" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B488" t="inlineStr" s="2">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="C488" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D488" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[2]</t>
+          <t xml:space="preserve">survivor.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E488" t="inlineStr" s="2">
@@ -16078,14 +16078,14 @@
       </c>
       <c r="F488" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で約束した勝利を、ちゃんと果たせました。これが私たちの誠意です</t>
+          <t xml:space="preserve">一人、受け止めました。…息は上がってますが、まだ役目の途中です。次、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="489" ht="40" customHeight="1">
       <c r="A489" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B489" t="inlineStr" s="2">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="D489" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[3]</t>
+          <t xml:space="preserve">champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E489" t="inlineStr" s="2">
@@ -16110,14 +16110,14 @@
       </c>
       <c r="F489" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた想いに応えられた。それが何より嬉しいです</t>
+          <t xml:space="preserve">託された順番を守り抜けました。仲間と団体に、この勝利を返せてよかったです</t>
         </is>
       </c>
     </row>
     <row r="490" ht="40" customHeight="1">
       <c r="A490" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B490" t="inlineStr" s="2">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="D490" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.earnest[1]</t>
+          <t xml:space="preserve">champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E490" t="inlineStr" s="2">
@@ -16142,14 +16142,14 @@
       </c>
       <c r="F490" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価はありがたいです。ただ、団体を勝たせられなかった。その悔しさを忘れません</t>
+          <t xml:space="preserve">三人で約束した勝利を、ちゃんと果たせました。これが私たちの誠意です</t>
         </is>
       </c>
     </row>
     <row r="491" ht="40" customHeight="1">
       <c r="A491" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B491" t="inlineStr" s="2">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="D491" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.earnest[2]</t>
+          <t xml:space="preserve">champion.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E491" t="inlineStr" s="2">
@@ -16174,14 +16174,14 @@
       </c>
       <c r="F491" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞に恥じない結果を、次は団体でも出します。必ず</t>
+          <t xml:space="preserve">仲間が繋いでくれた想いに応えられた。それが何より嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="492" ht="40" customHeight="1">
       <c r="A492" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B492" t="inlineStr" s="2">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="D492" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.earnest[3]</t>
+          <t xml:space="preserve">defiant.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E492" t="inlineStr" s="2">
@@ -16206,14 +16206,14 @@
       </c>
       <c r="F492" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間の分まで頑張れなかった。その責任を、次こそ果たします</t>
+          <t xml:space="preserve">評価はありがたいです。ただ、団体を勝たせられなかった。その悔しさを忘れません</t>
         </is>
       </c>
     </row>
     <row r="493" ht="40" customHeight="1">
       <c r="A493" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B493" t="inlineStr" s="2">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="D493" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.earnest[1]</t>
+          <t xml:space="preserve">defiant.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E493" t="inlineStr" s="2">
@@ -16238,14 +16238,14 @@
       </c>
       <c r="F493" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒れても次の仲間がいる。その安心があったから、私は何度でも立てました</t>
+          <t xml:space="preserve">この賞に恥じない結果を、次は団体でも出します。必ず</t>
         </is>
       </c>
     </row>
     <row r="494" ht="40" customHeight="1">
       <c r="A494" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B494" t="inlineStr" s="2">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="D494" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.earnest[2]</t>
+          <t xml:space="preserve">defiant.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E494" t="inlineStr" s="2">
@@ -16270,14 +16270,14 @@
       </c>
       <c r="F494" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人一人、正面から向き合いました。手を抜く理由なんてありませんから</t>
+          <t xml:space="preserve">仲間の分まで頑張れなかった。その責任を、次こそ果たします</t>
         </is>
       </c>
     </row>
     <row r="495" ht="40" customHeight="1">
       <c r="A495" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B495" t="inlineStr" s="2">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="D495" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.earnest[3]</t>
+          <t xml:space="preserve">gauntlet.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E495" t="inlineStr" s="2">
@@ -16302,14 +16302,14 @@
       </c>
       <c r="F495" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界だと思った瞬間が何度もありました。でも、ここで止まるわけにはいかなかったんです</t>
+          <t xml:space="preserve">倒れても次の仲間がいる。その安心があったから、私は何度でも立てました</t>
         </is>
       </c>
     </row>
     <row r="496" ht="40" customHeight="1">
       <c r="A496" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B496" t="inlineStr" s="2">
@@ -16319,12 +16319,12 @@
       </c>
       <c r="C496" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D496" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E496" t="inlineStr" s="2">
@@ -16334,14 +16334,14 @@
       </c>
       <c r="F496" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">支えてくれたみんなのおかげです…！</t>
+          <t xml:space="preserve">一人一人、正面から向き合いました。手を抜く理由なんてありませんから</t>
         </is>
       </c>
     </row>
     <row r="497" ht="40" customHeight="1">
       <c r="A497" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B497" t="inlineStr" s="2">
@@ -16351,12 +16351,12 @@
       </c>
       <c r="C497" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D497" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[2]</t>
+          <t xml:space="preserve">gauntlet.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E497" t="inlineStr" s="2">
@@ -16366,14 +16366,14 @@
       </c>
       <c r="F497" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…できた…。ありがとうございます…！</t>
+          <t xml:space="preserve">限界だと思った瞬間が何度もありました。でも、ここで止まるわけにはいかなかったんです</t>
         </is>
       </c>
     </row>
     <row r="498" ht="40" customHeight="1">
       <c r="A498" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B498" t="inlineStr" s="2">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="D498" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.earnest[1]</t>
+          <t xml:space="preserve">champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E498" t="inlineStr" s="2">
@@ -16398,14 +16398,14 @@
       </c>
       <c r="F498" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ないです…。もっと頑張ります…</t>
+          <t xml:space="preserve">支えてくれたみんなのおかげです…！</t>
         </is>
       </c>
     </row>
     <row r="499" ht="40" customHeight="1">
       <c r="A499" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B499" t="inlineStr" s="2">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="D499" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.earnest[2]</t>
+          <t xml:space="preserve">champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E499" t="inlineStr" s="2">
@@ -16430,14 +16430,14 @@
       </c>
       <c r="F499" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…けど、この悔しさを忘れない</t>
+          <t xml:space="preserve">優勝…できた…。ありがとうございます…！</t>
         </is>
       </c>
     </row>
     <row r="500" ht="40" customHeight="1">
       <c r="A500" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B500" t="inlineStr" s="2">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="D500" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.earnest[1]</t>
+          <t xml:space="preserve">postLose.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E500" t="inlineStr" s="2">
@@ -16462,14 +16462,14 @@
       </c>
       <c r="F500" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…！ でもまだ終わりじゃない</t>
+          <t xml:space="preserve">申し訳ないです…。もっと頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="501" ht="40" customHeight="1">
       <c r="A501" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B501" t="inlineStr" s="2">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="D501" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.earnest[2]</t>
+          <t xml:space="preserve">postLose.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E501" t="inlineStr" s="2">
@@ -16494,14 +16494,14 @@
       </c>
       <c r="F501" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一歩ずつ…次も全力で</t>
+          <t xml:space="preserve">悔しい…けど、この悔しさを忘れない</t>
         </is>
       </c>
     </row>
     <row r="502" ht="40" customHeight="1">
       <c r="A502" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B502" t="inlineStr" s="2">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="D502" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.earnest[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E502" t="inlineStr" s="2">
@@ -16526,14 +16526,14 @@
       </c>
       <c r="F502" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯やれました…！ この経験を活かしたい</t>
+          <t xml:space="preserve">勝てた…！ でもまだ終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="503" ht="40" customHeight="1">
       <c r="A503" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B503" t="inlineStr" s="2">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="D503" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.earnest[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E503" t="inlineStr" s="2">
@@ -16558,14 +16558,14 @@
       </c>
       <c r="F503" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔いのない大会でした。支えてくれた皆さんに感謝です</t>
+          <t xml:space="preserve">一歩ずつ…次も全力で</t>
         </is>
       </c>
     </row>
     <row r="504" ht="40" customHeight="1">
       <c r="A504" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B504" t="inlineStr" s="2">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="D504" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[1]</t>
+          <t xml:space="preserve">postWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E504" t="inlineStr" s="2">
@@ -16590,14 +16590,14 @@
       </c>
       <c r="F504" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この舞台に立てることが…嬉しい。だから全部出し切ります</t>
+          <t xml:space="preserve">精一杯やれました…！ この経験を活かしたい</t>
         </is>
       </c>
     </row>
     <row r="505" ht="40" customHeight="1">
       <c r="A505" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B505" t="inlineStr" s="2">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="D505" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[2]</t>
+          <t xml:space="preserve">postWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E505" t="inlineStr" s="2">
@@ -16622,14 +16622,14 @@
       </c>
       <c r="F505" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝…夢みたいです。でも、勝ちたい…！</t>
+          <t xml:space="preserve">悔いのない大会でした。支えてくれた皆さんに感謝です</t>
         </is>
       </c>
     </row>
     <row r="506" ht="40" customHeight="1">
       <c r="A506" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B506" t="inlineStr" s="2">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="D506" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E506" t="inlineStr" s="2">
@@ -16654,14 +16654,14 @@
       </c>
       <c r="F506" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どんな相手でも、やることは変わりません</t>
+          <t xml:space="preserve">この舞台に立てることが…嬉しい。だから全部出し切ります</t>
         </is>
       </c>
     </row>
     <row r="507" ht="40" customHeight="1">
       <c r="A507" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B507" t="inlineStr" s="2">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="D507" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E507" t="inlineStr" s="2">
@@ -16686,14 +16686,14 @@
       </c>
       <c r="F507" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦を大切に…全力で行きます</t>
+          <t xml:space="preserve">決勝…夢みたいです。でも、勝ちたい…！</t>
         </is>
       </c>
     </row>
     <row r="508" ht="40" customHeight="1">
       <c r="A508" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B508" t="inlineStr" s="2">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="D508" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.earnest[1]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E508" t="inlineStr" s="2">
@@ -16718,14 +16718,14 @@
       </c>
       <c r="F508" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯、やらせていただきます…！</t>
+          <t xml:space="preserve">どんな相手でも、やることは変わりません</t>
         </is>
       </c>
     </row>
     <row r="509" ht="40" customHeight="1">
       <c r="A509" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B509" t="inlineStr" s="2">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="D509" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.earnest[2]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E509" t="inlineStr" s="2">
@@ -16750,14 +16750,14 @@
       </c>
       <c r="F509" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ばれたからには…絶対に恥ずかしくない試合を</t>
+          <t xml:space="preserve">一戦一戦を大切に…全力で行きます</t>
         </is>
       </c>
     </row>
     <row r="510" ht="40" customHeight="1">
       <c r="A510" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B510" t="inlineStr" s="2">
@@ -16767,12 +16767,12 @@
       </c>
       <c r="C510" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D510" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">summon.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E510" t="inlineStr" s="2">
@@ -16782,14 +16782,14 @@
       </c>
       <c r="F510" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い全力で…最高の舞台だもの</t>
+          <t xml:space="preserve">精一杯、やらせていただきます…！</t>
         </is>
       </c>
     </row>
     <row r="511" ht="40" customHeight="1">
       <c r="A511" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B511" t="inlineStr" s="2">
@@ -16799,12 +16799,12 @@
       </c>
       <c r="C511" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D511" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">summon.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E511" t="inlineStr" s="2">
@@ -16814,14 +16814,14 @@
       </c>
       <c r="F511" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この対戦、ずっと待ってました</t>
+          <t xml:space="preserve">選ばれたからには…絶対に恥ずかしくない試合を</t>
         </is>
       </c>
     </row>
     <row r="512" ht="40" customHeight="1">
       <c r="A512" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B512" t="inlineStr" s="2">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="C512" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D512" t="inlineStr" s="12">
@@ -16846,14 +16846,14 @@
       </c>
       <c r="F512" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆さんのおかげです。ありがとうございます……！</t>
+          <t xml:space="preserve">お互い全力で…最高の舞台だもの</t>
         </is>
       </c>
     </row>
     <row r="513" ht="40" customHeight="1">
       <c r="A513" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B513" t="inlineStr" s="2">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="C513" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D513" t="inlineStr" s="12">
@@ -16878,14 +16878,14 @@
       </c>
       <c r="F513" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習してきたことが、全部報われた気がします……！</t>
+          <t xml:space="preserve">この対戦、ずっと待ってました</t>
         </is>
       </c>
     </row>
     <row r="514" ht="40" customHeight="1">
       <c r="A514" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.earnest[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B514" t="inlineStr" s="2">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="C514" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D514" t="inlineStr" s="12">
@@ -16910,14 +16910,14 @@
       </c>
       <c r="F514" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらの団体の実力、確かめさせてもらいます</t>
+          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆さんのおかげです。ありがとうございます……！</t>
         </is>
       </c>
     </row>
     <row r="515" ht="40" customHeight="1">
       <c r="A515" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.earnest[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B515" t="inlineStr" s="2">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="C515" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D515" t="inlineStr" s="12">
@@ -16942,14 +16942,14 @@
       </c>
       <c r="F515" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正々堂々、全力でぶつかります。逃げないでくださいね</t>
+          <t xml:space="preserve">練習してきたことが、全部報われた気がします……！</t>
         </is>
       </c>
     </row>
     <row r="516" ht="40" customHeight="1">
       <c r="A516" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B516" t="inlineStr" s="2">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C516" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D516" t="inlineStr" s="12">
@@ -16974,14 +16974,14 @@
       </c>
       <c r="F516" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念です。正々堂々の勝負がしたかった</t>
+          <t xml:space="preserve">そちらの団体の実力、確かめさせてもらいます</t>
         </is>
       </c>
     </row>
     <row r="517" ht="40" customHeight="1">
       <c r="A517" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B517" t="inlineStr" s="2">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="C517" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D517" t="inlineStr" s="12">
@@ -17006,14 +17006,14 @@
       </c>
       <c r="F517" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは受けてください。待っています</t>
+          <t xml:space="preserve">正々堂々、全力でぶつかります。逃げないでくださいね</t>
         </is>
       </c>
     </row>
     <row r="518" ht="40" customHeight="1">
       <c r="A518" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B518" t="inlineStr" s="2">
@@ -17023,12 +17023,12 @@
       </c>
       <c r="C518" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D518" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E518" t="inlineStr" s="2">
@@ -17038,14 +17038,14 @@
       </c>
       <c r="F518" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力が足りませんでした…。もっと練習して、必ず強くなります</t>
+          <t xml:space="preserve">残念です。正々堂々の勝負がしたかった</t>
         </is>
       </c>
     </row>
     <row r="519" ht="40" customHeight="1">
       <c r="A519" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B519" t="inlineStr" s="2">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="C519" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D519" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E519" t="inlineStr" s="2">
@@ -17070,14 +17070,14 @@
       </c>
       <c r="F519" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…でも、この経験を無駄にしない</t>
+          <t xml:space="preserve">次こそは受けてください。待っています</t>
         </is>
       </c>
     </row>
     <row r="520" ht="40" customHeight="1">
       <c r="A520" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B520" t="inlineStr" s="2">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="D520" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.earnest[1]</t>
+          <t xml:space="preserve">result_lose.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E520" t="inlineStr" s="2">
@@ -17102,14 +17102,14 @@
       </c>
       <c r="F520" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました…！ みんなの頑張りが実った結果です</t>
+          <t xml:space="preserve">力が足りませんでした…。もっと練習して、必ず強くなります</t>
         </is>
       </c>
     </row>
     <row r="521" ht="40" customHeight="1">
       <c r="A521" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B521" t="inlineStr" s="2">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="D521" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.earnest[2]</t>
+          <t xml:space="preserve">result_lose.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E521" t="inlineStr" s="2">
@@ -17134,14 +17134,14 @@
       </c>
       <c r="F521" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦でした。相手にも感謝です</t>
+          <t xml:space="preserve">悔しい…でも、この経験を無駄にしない</t>
         </is>
       </c>
     </row>
     <row r="522" ht="40" customHeight="1">
       <c r="A522" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B522" t="inlineStr" s="2">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="C522" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D522" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">result_win.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E522" t="inlineStr" s="2">
@@ -17166,14 +17166,14 @@
       </c>
       <c r="F522" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…！ みんなのために、絶対に負けたくなかったから…！</t>
+          <t xml:space="preserve">勝てました…！ みんなの頑張りが実った結果です</t>
         </is>
       </c>
     </row>
     <row r="523" ht="40" customHeight="1">
       <c r="A523" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B523" t="inlineStr" s="2">
@@ -17183,12 +17183,12 @@
       </c>
       <c r="C523" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D523" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">result_win.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E523" t="inlineStr" s="2">
@@ -17198,14 +17198,14 @@
       </c>
       <c r="F523" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名前を背負って戦えて…嬉しい。勝ててもっと嬉しい…！</t>
+          <t xml:space="preserve">いい対抗戦でした。相手にも感謝です</t>
         </is>
       </c>
     </row>
     <row r="524" ht="40" customHeight="1">
       <c r="A524" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B524" t="inlineStr" s="2">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="D524" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[3]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E524" t="inlineStr" s="2">
@@ -17230,14 +17230,14 @@
       </c>
       <c r="F524" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で戦いました…！ 団体のみんなに恥じない試合ができたなら…</t>
+          <t xml:space="preserve">勝てた…！ みんなのために、絶対に負けたくなかったから…！</t>
         </is>
       </c>
     </row>
     <row r="525" ht="40" customHeight="1">
       <c r="A525" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B525" t="inlineStr" s="2">
@@ -17247,29 +17247,29 @@
       </c>
       <c r="C525" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D525" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E525" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F525" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習してきたことが全部報われた。泣きそう</t>
+          <t xml:space="preserve">団体の名前を背負って戦えて…嬉しい。勝ててもっと嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="526" ht="40" customHeight="1">
       <c r="A526" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B526" t="inlineStr" s="2">
@@ -17279,29 +17279,29 @@
       </c>
       <c r="C526" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D526" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E526" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F526" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの時辞めなくてよかった。この瞬間のために全部あったんだ</t>
+          <t xml:space="preserve">全力で戦いました…！ 団体のみんなに恥じない試合ができたなら…</t>
         </is>
       </c>
     </row>
     <row r="527" ht="40" customHeight="1">
       <c r="A527" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B527" t="inlineStr" s="2">
@@ -17311,29 +17311,29 @@
       </c>
       <c r="C527" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D527" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">fighter.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E527" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F527" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度チャンスをもらえた。無駄にしません</t>
+          <t xml:space="preserve">練習してきたことが全部報われた。泣きそう</t>
         </is>
       </c>
     </row>
     <row r="528" ht="40" customHeight="1">
       <c r="A528" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B528" t="inlineStr" s="2">
@@ -17343,29 +17343,29 @@
       </c>
       <c r="C528" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D528" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">fighter.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E528" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F528" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれた恩は、練習の量でお返しします</t>
+          <t xml:space="preserve">あの時辞めなくてよかった。この瞬間のために全部あったんだ</t>
         </is>
       </c>
     </row>
     <row r="529" ht="40" customHeight="1">
       <c r="A529" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B529" t="inlineStr" s="2">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="C529" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D529" t="inlineStr" s="12">
@@ -17390,44 +17390,108 @@
       </c>
       <c r="F529" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ていてくれた人がいた。それだけで頑張れます</t>
+          <t xml:space="preserve">もう一度チャンスをもらえた。無駄にしません</t>
         </is>
       </c>
     </row>
     <row r="530" ht="40" customHeight="1">
       <c r="A530" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくれた恩には、積み上げた練習で応えます</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="40" customHeight="1">
+      <c r="A531" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見ていてくれた人がいた。それだけで頑張れます</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="40" customHeight="1">
+      <c r="A532" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.earnest[2]</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr" s="2">
+      <c r="B532" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr" s="12">
+      <c r="D532" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr" s="2">
+      <c r="E532" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr" s="3">
+      <c r="F532" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">期待してもらった分、毎日積み上げていきます</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H530"/>
+  <autoFilter ref="A1:H532"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×真面目.xlsx
@@ -438,7 +438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H532"/>
+  <dimension ref="A1:H534"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -15285,7 +15285,7 @@
     <row r="464" ht="40" customHeight="1">
       <c r="A464" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B464" t="inlineStr" s="2">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="D464" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E464" t="inlineStr" s="2">
@@ -15310,14 +15310,14 @@
       </c>
       <c r="F464" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一つ一つの練習を大切に。基礎が全ての土台だ</t>
+          <t xml:space="preserve">私情を持ち込むな、と自分に言い聞かせているが…難しい</t>
         </is>
       </c>
     </row>
     <row r="465" ht="40" customHeight="1">
       <c r="A465" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B465" t="inlineStr" s="2">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="D465" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E465" t="inlineStr" s="2">
@@ -15342,14 +15342,14 @@
       </c>
       <c r="F465" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のメニューも全力でこなす。手は抜かない</t>
+          <t xml:space="preserve">集中できていない自分が、情けない…</t>
         </is>
       </c>
     </row>
     <row r="466" ht="40" customHeight="1">
       <c r="A466" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B466" t="inlineStr" s="2">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="D466" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-02.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E466" t="inlineStr" s="2">
@@ -15374,14 +15374,14 @@
       </c>
       <c r="F466" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何か改善すべき点があるなら教えてほしい…</t>
+          <t xml:space="preserve">一つ一つの練習を大切に。基礎が全ての土台だ</t>
         </is>
       </c>
     </row>
     <row r="467" ht="40" customHeight="1">
       <c r="A467" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B467" t="inlineStr" s="2">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="D467" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-02.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E467" t="inlineStr" s="2">
@@ -15406,14 +15406,14 @@
       </c>
       <c r="F467" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信頼に応えるよう、より一層精進します</t>
+          <t xml:space="preserve">今日のメニューも全力でこなす。手は抜かない</t>
         </is>
       </c>
     </row>
     <row r="468" ht="40" customHeight="1">
       <c r="A468" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B468" t="inlineStr" s="2">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="D468" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E468" t="inlineStr" s="2">
@@ -15438,14 +15438,14 @@
       </c>
       <c r="F468" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切磋琢磨できる環境に感謝してる</t>
+          <t xml:space="preserve">何か改善すべき点があるなら教えてほしい…</t>
         </is>
       </c>
     </row>
     <row r="469" ht="40" customHeight="1">
       <c r="A469" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B469" t="inlineStr" s="2">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="D469" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E469" t="inlineStr" s="2">
@@ -15470,14 +15470,14 @@
       </c>
       <c r="F469" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">意識するからこそ成長できる</t>
+          <t xml:space="preserve">信頼に応えるよう、より一層精進します</t>
         </is>
       </c>
     </row>
     <row r="470" ht="40" customHeight="1">
       <c r="A470" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B470" t="inlineStr" s="2">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="D470" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-04.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E470" t="inlineStr" s="2">
@@ -15502,14 +15502,14 @@
       </c>
       <c r="F470" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場できなかった…次こそは選んでもらえるように頑張らないと</t>
+          <t xml:space="preserve">切磋琢磨できる環境に感謝してる</t>
         </is>
       </c>
     </row>
     <row r="471" ht="40" customHeight="1">
       <c r="A471" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B471" t="inlineStr" s="2">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="D471" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-05.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E471" t="inlineStr" s="2">
@@ -15534,14 +15534,14 @@
       </c>
       <c r="F471" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力不足なら練習で補う。必ず次は出場する</t>
+          <t xml:space="preserve">意識するからこそ成長できる</t>
         </is>
       </c>
     </row>
     <row r="472" ht="40" customHeight="1">
       <c r="A472" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B472" t="inlineStr" s="2">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="D472" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-06.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E472" t="inlineStr" s="2">
@@ -15566,14 +15566,14 @@
       </c>
       <c r="F472" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コンディションが良くない。焦らず回復に努めよう</t>
+          <t xml:space="preserve">出場できなかった…次こそは選んでもらえるように頑張らないと</t>
         </is>
       </c>
     </row>
     <row r="473" ht="40" customHeight="1">
       <c r="A473" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B473" t="inlineStr" s="2">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="D473" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-06.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E473" t="inlineStr" s="2">
@@ -15598,14 +15598,14 @@
       </c>
       <c r="F473" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗の原因を見つけなければ。何かが間違っているはずだ</t>
+          <t xml:space="preserve">実力不足なら練習で補う。必ず次は出場する</t>
         </is>
       </c>
     </row>
     <row r="474" ht="40" customHeight="1">
       <c r="A474" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B474" t="inlineStr" s="2">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="D474" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-07.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E474" t="inlineStr" s="2">
@@ -15630,14 +15630,14 @@
       </c>
       <c r="F474" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けが続いている。でも腐らない。必ず糸口はある</t>
+          <t xml:space="preserve">コンディションが良くない。焦らず回復に努めよう</t>
         </is>
       </c>
     </row>
     <row r="475" ht="40" customHeight="1">
       <c r="A475" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B475" t="inlineStr" s="2">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="D475" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-08.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E475" t="inlineStr" s="2">
@@ -15662,14 +15662,14 @@
       </c>
       <c r="F475" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝は努力の証。でも油断はしない。謙虚にいこう</t>
+          <t xml:space="preserve">連敗の原因を見つけなければ。何かが間違っているはずだ</t>
         </is>
       </c>
     </row>
     <row r="476" ht="40" customHeight="1">
       <c r="A476" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B476" t="inlineStr" s="2">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="D476" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.earnest[1]</t>
+          <t xml:space="preserve">GL-08.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E476" t="inlineStr" s="2">
@@ -15694,14 +15694,14 @@
       </c>
       <c r="F476" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リハビリに全力で取り組む。一日でも早く復帰する</t>
+          <t xml:space="preserve">負けが続いている。でも腐らない。必ず糸口はある</t>
         </is>
       </c>
     </row>
     <row r="477" ht="40" customHeight="1">
       <c r="A477" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B477" t="inlineStr" s="2">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="D477" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.earnest[2]</t>
+          <t xml:space="preserve">GL-09.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E477" t="inlineStr" s="2">
@@ -15726,14 +15726,14 @@
       </c>
       <c r="F477" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我の間もできることはある。頭を鍛える時間にする</t>
+          <t xml:space="preserve">連勝は努力の証。でも油断はしない。謙虚にいこう</t>
         </is>
       </c>
     </row>
     <row r="478" ht="40" customHeight="1">
       <c r="A478" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B478" t="inlineStr" s="2">
@@ -15743,12 +15743,12 @@
       </c>
       <c r="C478" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D478" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">GL-10.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E478" t="inlineStr" s="2">
@@ -15758,14 +15758,14 @@
       </c>
       <c r="F478" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調は終わったけど…あの期間で掴んだものがある</t>
+          <t xml:space="preserve">リハビリに全力で取り組む。一日でも早く復帰する</t>
         </is>
       </c>
     </row>
     <row r="479" ht="40" customHeight="1">
       <c r="A479" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B479" t="inlineStr" s="2">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="C479" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D479" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">GL-10.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E479" t="inlineStr" s="2">
@@ -15790,14 +15790,14 @@
       </c>
       <c r="F479" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの好調は偶然じゃない。努力の結果だ。また必ず来る</t>
+          <t xml:space="preserve">怪我の間もできることはある。頭を鍛える時間にする</t>
         </is>
       </c>
     </row>
     <row r="480" ht="40" customHeight="1">
       <c r="A480" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B480" t="inlineStr" s="2">
@@ -15807,29 +15807,29 @@
       </c>
       <c r="C480" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D480" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E480" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F480" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでもらった。最後は、私が全部背負って立ちます</t>
+          <t xml:space="preserve">絶好調は終わったけど…あの期間で掴んだものがある</t>
         </is>
       </c>
     </row>
     <row r="481" ht="40" customHeight="1">
       <c r="A481" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B481" t="inlineStr" s="2">
@@ -15839,29 +15839,29 @@
       </c>
       <c r="C481" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D481" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E481" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F481" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は限界です。でも、託された役目を、途中で降りるわけにはいきません</t>
+          <t xml:space="preserve">あの好調は偶然じゃない。努力の結果だ。また必ず来る</t>
         </is>
       </c>
     </row>
     <row r="482" ht="40" customHeight="1">
       <c r="A482" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B482" t="inlineStr" s="2">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="D482" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[3]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E482" t="inlineStr" s="2">
@@ -15886,14 +15886,14 @@
       </c>
       <c r="F482" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけでも、この一戦だけは譲れません。全部、出し切ります</t>
+          <t xml:space="preserve">ここまで繋いでもらった。最後は、私が全部背負って立ちます</t>
         </is>
       </c>
     </row>
     <row r="483" ht="40" customHeight="1">
       <c r="A483" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B483" t="inlineStr" s="2">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="D483" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E483" t="inlineStr" s="2">
@@ -15918,14 +15918,14 @@
       </c>
       <c r="F483" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どんな相手でも、全力で。仲間に繋ぐ、それだけは絶対です</t>
+          <t xml:space="preserve">身体は限界です。でも、託された役目を、途中で降りるわけにはいきません</t>
         </is>
       </c>
     </row>
     <row r="484" ht="40" customHeight="1">
       <c r="A484" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B484" t="inlineStr" s="2">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="D484" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E484" t="inlineStr" s="2">
@@ -15950,14 +15950,14 @@
       </c>
       <c r="F484" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目の前の一戦から、正面で受けます。手を抜く理由がありません</t>
+          <t xml:space="preserve">傷だらけでも、この一戦だけは譲れません。全部、出し切ります</t>
         </is>
       </c>
     </row>
     <row r="485" ht="40" customHeight="1">
       <c r="A485" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B485" t="inlineStr" s="2">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="D485" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[3]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E485" t="inlineStr" s="2">
@@ -15982,14 +15982,14 @@
       </c>
       <c r="F485" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、確実に。託されたものを、途中で放り出せませんから</t>
+          <t xml:space="preserve">どんな相手でも、全力で。仲間に繋ぐ、それだけは絶対です</t>
         </is>
       </c>
     </row>
     <row r="486" ht="40" customHeight="1">
       <c r="A486" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B486" t="inlineStr" s="2">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="D486" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.earnest[1]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E486" t="inlineStr" s="2">
@@ -16014,14 +16014,14 @@
       </c>
       <c r="F486" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒しました。…はぁ、まだ退けません。繋ぐまで、ここは渡さない。次、来てください</t>
+          <t xml:space="preserve">目の前の一戦から、正面で受けます。手を抜く理由がありません</t>
         </is>
       </c>
     </row>
     <row r="487" ht="40" customHeight="1">
       <c r="A487" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B487" t="inlineStr" s="2">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="D487" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.earnest[2]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E487" t="inlineStr" s="2">
@@ -16046,14 +16046,14 @@
       </c>
       <c r="F487" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。託された役目、途中で放り出せない。次の相手、来てください</t>
+          <t xml:space="preserve">一戦ずつ、確実に。託されたものを、途中で放り出せませんから</t>
         </is>
       </c>
     </row>
     <row r="488" ht="40" customHeight="1">
       <c r="A488" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B488" t="inlineStr" s="2">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="D488" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.earnest[3]</t>
+          <t xml:space="preserve">survivor.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E488" t="inlineStr" s="2">
@@ -16078,14 +16078,14 @@
       </c>
       <c r="F488" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、受け止めました。…息は上がってますが、まだ役目の途中です。次、どうぞ</t>
+          <t xml:space="preserve">一人、倒しました。…はぁ、まだ退けません。繋ぐまで、ここは渡さない。次、来てください</t>
         </is>
       </c>
     </row>
     <row r="489" ht="40" customHeight="1">
       <c r="A489" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B489" t="inlineStr" s="2">
@@ -16095,12 +16095,12 @@
       </c>
       <c r="C489" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D489" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[1]</t>
+          <t xml:space="preserve">survivor.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E489" t="inlineStr" s="2">
@@ -16110,14 +16110,14 @@
       </c>
       <c r="F489" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">託された順番を守り抜けました。仲間と団体に、この勝利を返せてよかったです</t>
+          <t xml:space="preserve">まだ立ってます。託された役目、途中で放り出せない。次の相手、来てください</t>
         </is>
       </c>
     </row>
     <row r="490" ht="40" customHeight="1">
       <c r="A490" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B490" t="inlineStr" s="2">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="C490" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D490" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[2]</t>
+          <t xml:space="preserve">survivor.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E490" t="inlineStr" s="2">
@@ -16142,14 +16142,14 @@
       </c>
       <c r="F490" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で約束した勝利を、ちゃんと果たせました。これが私たちの誠意です</t>
+          <t xml:space="preserve">一人、受け止めました。…息は上がってますが、まだ役目の途中です。次、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="491" ht="40" customHeight="1">
       <c r="A491" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B491" t="inlineStr" s="2">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="D491" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[3]</t>
+          <t xml:space="preserve">champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E491" t="inlineStr" s="2">
@@ -16174,14 +16174,14 @@
       </c>
       <c r="F491" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた想いに応えられた。それが何より嬉しいです</t>
+          <t xml:space="preserve">託された順番を守り抜けました。仲間と団体に、この勝利を返せてよかったです</t>
         </is>
       </c>
     </row>
     <row r="492" ht="40" customHeight="1">
       <c r="A492" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B492" t="inlineStr" s="2">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="D492" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.earnest[1]</t>
+          <t xml:space="preserve">champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E492" t="inlineStr" s="2">
@@ -16206,14 +16206,14 @@
       </c>
       <c r="F492" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価はありがたいです。ただ、団体を勝たせられなかった。その悔しさを忘れません</t>
+          <t xml:space="preserve">三人で約束した勝利を、ちゃんと果たせました。これが私たちの誠意です</t>
         </is>
       </c>
     </row>
     <row r="493" ht="40" customHeight="1">
       <c r="A493" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B493" t="inlineStr" s="2">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="D493" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.earnest[2]</t>
+          <t xml:space="preserve">champion.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E493" t="inlineStr" s="2">
@@ -16238,14 +16238,14 @@
       </c>
       <c r="F493" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞に恥じない結果を、次は団体でも出します。必ず</t>
+          <t xml:space="preserve">仲間が繋いでくれた想いに応えられた。それが何より嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="494" ht="40" customHeight="1">
       <c r="A494" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B494" t="inlineStr" s="2">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="D494" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.earnest[3]</t>
+          <t xml:space="preserve">defiant.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E494" t="inlineStr" s="2">
@@ -16270,14 +16270,14 @@
       </c>
       <c r="F494" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間の分まで頑張れなかった。その責任を、次こそ果たします</t>
+          <t xml:space="preserve">評価はありがたいです。ただ、団体を勝たせられなかった。その悔しさを忘れません</t>
         </is>
       </c>
     </row>
     <row r="495" ht="40" customHeight="1">
       <c r="A495" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B495" t="inlineStr" s="2">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="D495" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.earnest[1]</t>
+          <t xml:space="preserve">defiant.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E495" t="inlineStr" s="2">
@@ -16302,14 +16302,14 @@
       </c>
       <c r="F495" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒れても次の仲間がいる。その安心があったから、私は何度でも立てました</t>
+          <t xml:space="preserve">この賞に恥じない結果を、次は団体でも出します。必ず</t>
         </is>
       </c>
     </row>
     <row r="496" ht="40" customHeight="1">
       <c r="A496" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B496" t="inlineStr" s="2">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="D496" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.earnest[2]</t>
+          <t xml:space="preserve">defiant.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E496" t="inlineStr" s="2">
@@ -16334,14 +16334,14 @@
       </c>
       <c r="F496" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人一人、正面から向き合いました。手を抜く理由なんてありませんから</t>
+          <t xml:space="preserve">仲間の分まで頑張れなかった。その責任を、次こそ果たします</t>
         </is>
       </c>
     </row>
     <row r="497" ht="40" customHeight="1">
       <c r="A497" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B497" t="inlineStr" s="2">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="D497" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.earnest[3]</t>
+          <t xml:space="preserve">gauntlet.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E497" t="inlineStr" s="2">
@@ -16366,14 +16366,14 @@
       </c>
       <c r="F497" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界だと思った瞬間が何度もありました。でも、ここで止まるわけにはいかなかったんです</t>
+          <t xml:space="preserve">倒れても次の仲間がいる。その安心があったから、私は何度でも立てました</t>
         </is>
       </c>
     </row>
     <row r="498" ht="40" customHeight="1">
       <c r="A498" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B498" t="inlineStr" s="2">
@@ -16383,12 +16383,12 @@
       </c>
       <c r="C498" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D498" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E498" t="inlineStr" s="2">
@@ -16398,14 +16398,14 @@
       </c>
       <c r="F498" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">支えてくれたみんなのおかげです…！</t>
+          <t xml:space="preserve">一人一人、正面から向き合いました。手を抜く理由なんてありませんから</t>
         </is>
       </c>
     </row>
     <row r="499" ht="40" customHeight="1">
       <c r="A499" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B499" t="inlineStr" s="2">
@@ -16415,12 +16415,12 @@
       </c>
       <c r="C499" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D499" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.earnest[2]</t>
+          <t xml:space="preserve">gauntlet.standard.earnest[3]</t>
         </is>
       </c>
       <c r="E499" t="inlineStr" s="2">
@@ -16430,14 +16430,14 @@
       </c>
       <c r="F499" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…できた…。ありがとうございます…！</t>
+          <t xml:space="preserve">限界だと思った瞬間が何度もありました。でも、ここで止まるわけにはいかなかったんです</t>
         </is>
       </c>
     </row>
     <row r="500" ht="40" customHeight="1">
       <c r="A500" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B500" t="inlineStr" s="2">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="D500" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.earnest[1]</t>
+          <t xml:space="preserve">champion.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E500" t="inlineStr" s="2">
@@ -16462,14 +16462,14 @@
       </c>
       <c r="F500" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ないです…。もっと頑張ります…</t>
+          <t xml:space="preserve">支えてくれたみんなのおかげです…！</t>
         </is>
       </c>
     </row>
     <row r="501" ht="40" customHeight="1">
       <c r="A501" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B501" t="inlineStr" s="2">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="D501" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.earnest[2]</t>
+          <t xml:space="preserve">champion.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E501" t="inlineStr" s="2">
@@ -16494,14 +16494,14 @@
       </c>
       <c r="F501" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…けど、この悔しさを忘れない</t>
+          <t xml:space="preserve">優勝…できた…。ありがとうございます…！</t>
         </is>
       </c>
     </row>
     <row r="502" ht="40" customHeight="1">
       <c r="A502" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B502" t="inlineStr" s="2">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="D502" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.earnest[1]</t>
+          <t xml:space="preserve">postLose.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E502" t="inlineStr" s="2">
@@ -16526,14 +16526,14 @@
       </c>
       <c r="F502" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…！ でもまだ終わりじゃない</t>
+          <t xml:space="preserve">申し訳ないです…。もっと頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="503" ht="40" customHeight="1">
       <c r="A503" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B503" t="inlineStr" s="2">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="D503" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.earnest[2]</t>
+          <t xml:space="preserve">postLose.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E503" t="inlineStr" s="2">
@@ -16558,14 +16558,14 @@
       </c>
       <c r="F503" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一歩ずつ…次も全力で</t>
+          <t xml:space="preserve">悔しい…けど、この悔しさを忘れない</t>
         </is>
       </c>
     </row>
     <row r="504" ht="40" customHeight="1">
       <c r="A504" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B504" t="inlineStr" s="2">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="D504" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.earnest[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E504" t="inlineStr" s="2">
@@ -16590,14 +16590,14 @@
       </c>
       <c r="F504" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯やれました…！ この経験を活かしたい</t>
+          <t xml:space="preserve">勝てた…！ でもまだ終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="505" ht="40" customHeight="1">
       <c r="A505" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B505" t="inlineStr" s="2">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="D505" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.earnest[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E505" t="inlineStr" s="2">
@@ -16622,14 +16622,14 @@
       </c>
       <c r="F505" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔いのない大会でした。支えてくれた皆さんに感謝です</t>
+          <t xml:space="preserve">一歩ずつ…次も全力で</t>
         </is>
       </c>
     </row>
     <row r="506" ht="40" customHeight="1">
       <c r="A506" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B506" t="inlineStr" s="2">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="D506" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[1]</t>
+          <t xml:space="preserve">postWin.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E506" t="inlineStr" s="2">
@@ -16654,14 +16654,14 @@
       </c>
       <c r="F506" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この舞台に立てることが…嬉しい。だから全部出し切ります</t>
+          <t xml:space="preserve">精一杯やれました…！ この経験を活かしたい</t>
         </is>
       </c>
     </row>
     <row r="507" ht="40" customHeight="1">
       <c r="A507" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B507" t="inlineStr" s="2">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="D507" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.earnest[2]</t>
+          <t xml:space="preserve">postWin.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E507" t="inlineStr" s="2">
@@ -16686,14 +16686,14 @@
       </c>
       <c r="F507" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝…夢みたいです。でも、勝ちたい…！</t>
+          <t xml:space="preserve">悔いのない大会でした。支えてくれた皆さんに感謝です</t>
         </is>
       </c>
     </row>
     <row r="508" ht="40" customHeight="1">
       <c r="A508" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B508" t="inlineStr" s="2">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="D508" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[1]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E508" t="inlineStr" s="2">
@@ -16718,14 +16718,14 @@
       </c>
       <c r="F508" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どんな相手でも、やることは変わりません</t>
+          <t xml:space="preserve">この舞台に立てることが…嬉しい。だから全部出し切ります</t>
         </is>
       </c>
     </row>
     <row r="509" ht="40" customHeight="1">
       <c r="A509" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B509" t="inlineStr" s="2">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="D509" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.earnest[2]</t>
+          <t xml:space="preserve">preFinal.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E509" t="inlineStr" s="2">
@@ -16750,14 +16750,14 @@
       </c>
       <c r="F509" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦を大切に…全力で行きます</t>
+          <t xml:space="preserve">決勝…夢みたいです。でも、勝ちたい…！</t>
         </is>
       </c>
     </row>
     <row r="510" ht="40" customHeight="1">
       <c r="A510" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B510" t="inlineStr" s="2">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="D510" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.earnest[1]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E510" t="inlineStr" s="2">
@@ -16782,14 +16782,14 @@
       </c>
       <c r="F510" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯、やらせていただきます…！</t>
+          <t xml:space="preserve">どんな相手でも、やることは変わりません</t>
         </is>
       </c>
     </row>
     <row r="511" ht="40" customHeight="1">
       <c r="A511" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B511" t="inlineStr" s="2">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="D511" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.earnest[2]</t>
+          <t xml:space="preserve">preMatch.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E511" t="inlineStr" s="2">
@@ -16814,14 +16814,14 @@
       </c>
       <c r="F511" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ばれたからには…絶対に恥ずかしくない試合を</t>
+          <t xml:space="preserve">一戦一戦を大切に…全力で行きます</t>
         </is>
       </c>
     </row>
     <row r="512" ht="40" customHeight="1">
       <c r="A512" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B512" t="inlineStr" s="2">
@@ -16831,12 +16831,12 @@
       </c>
       <c r="C512" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D512" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">summon.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E512" t="inlineStr" s="2">
@@ -16846,14 +16846,14 @@
       </c>
       <c r="F512" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い全力で…最高の舞台だもの</t>
+          <t xml:space="preserve">精一杯、やらせていただきます…！</t>
         </is>
       </c>
     </row>
     <row r="513" ht="40" customHeight="1">
       <c r="A513" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B513" t="inlineStr" s="2">
@@ -16863,12 +16863,12 @@
       </c>
       <c r="C513" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D513" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">summon.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E513" t="inlineStr" s="2">
@@ -16878,14 +16878,14 @@
       </c>
       <c r="F513" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この対戦、ずっと待ってました</t>
+          <t xml:space="preserve">選ばれたからには…絶対に恥ずかしくない試合を</t>
         </is>
       </c>
     </row>
     <row r="514" ht="40" customHeight="1">
       <c r="A514" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B514" t="inlineStr" s="2">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="C514" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D514" t="inlineStr" s="12">
@@ -16910,14 +16910,14 @@
       </c>
       <c r="F514" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆さんのおかげです。ありがとうございます……！</t>
+          <t xml:space="preserve">お互い全力で…最高の舞台だもの</t>
         </is>
       </c>
     </row>
     <row r="515" ht="40" customHeight="1">
       <c r="A515" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B515" t="inlineStr" s="2">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="C515" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D515" t="inlineStr" s="12">
@@ -16942,14 +16942,14 @@
       </c>
       <c r="F515" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習してきたことが、全部報われた気がします……！</t>
+          <t xml:space="preserve">この対戦、ずっと待ってました</t>
         </is>
       </c>
     </row>
     <row r="516" ht="40" customHeight="1">
       <c r="A516" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.earnest[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B516" t="inlineStr" s="2">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C516" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D516" t="inlineStr" s="12">
@@ -16974,14 +16974,14 @@
       </c>
       <c r="F516" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらの団体の実力、確かめさせてもらいます</t>
+          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆さんのおかげです。ありがとうございます……！</t>
         </is>
       </c>
     </row>
     <row r="517" ht="40" customHeight="1">
       <c r="A517" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.earnest[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B517" t="inlineStr" s="2">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="C517" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D517" t="inlineStr" s="12">
@@ -17006,14 +17006,14 @@
       </c>
       <c r="F517" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正々堂々、全力でぶつかります。逃げないでくださいね</t>
+          <t xml:space="preserve">練習してきたことが、全部報われた気がします……！</t>
         </is>
       </c>
     </row>
     <row r="518" ht="40" customHeight="1">
       <c r="A518" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B518" t="inlineStr" s="2">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="C518" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D518" t="inlineStr" s="12">
@@ -17038,14 +17038,14 @@
       </c>
       <c r="F518" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念です。正々堂々の勝負がしたかった</t>
+          <t xml:space="preserve">そちらの団体の実力、確かめさせてもらいます</t>
         </is>
       </c>
     </row>
     <row r="519" ht="40" customHeight="1">
       <c r="A519" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B519" t="inlineStr" s="2">
@@ -17055,7 +17055,7 @@
       </c>
       <c r="C519" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D519" t="inlineStr" s="12">
@@ -17070,14 +17070,14 @@
       </c>
       <c r="F519" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは受けてください。待っています</t>
+          <t xml:space="preserve">正々堂々、全力でぶつかります。逃げないでくださいね</t>
         </is>
       </c>
     </row>
     <row r="520" ht="40" customHeight="1">
       <c r="A520" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B520" t="inlineStr" s="2">
@@ -17087,12 +17087,12 @@
       </c>
       <c r="C520" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D520" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E520" t="inlineStr" s="2">
@@ -17102,14 +17102,14 @@
       </c>
       <c r="F520" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力が足りませんでした…。もっと練習して、必ず強くなります</t>
+          <t xml:space="preserve">残念です。正々堂々の勝負がしたかった</t>
         </is>
       </c>
     </row>
     <row r="521" ht="40" customHeight="1">
       <c r="A521" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B521" t="inlineStr" s="2">
@@ -17119,12 +17119,12 @@
       </c>
       <c r="C521" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D521" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E521" t="inlineStr" s="2">
@@ -17134,14 +17134,14 @@
       </c>
       <c r="F521" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…でも、この経験を無駄にしない</t>
+          <t xml:space="preserve">次こそは受けてください。待っています</t>
         </is>
       </c>
     </row>
     <row r="522" ht="40" customHeight="1">
       <c r="A522" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B522" t="inlineStr" s="2">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="D522" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.earnest[1]</t>
+          <t xml:space="preserve">result_lose.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E522" t="inlineStr" s="2">
@@ -17166,14 +17166,14 @@
       </c>
       <c r="F522" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました…！ みんなの頑張りが実った結果です</t>
+          <t xml:space="preserve">力が足りませんでした…。もっと練習して、必ず強くなります</t>
         </is>
       </c>
     </row>
     <row r="523" ht="40" customHeight="1">
       <c r="A523" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B523" t="inlineStr" s="2">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="D523" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.earnest[2]</t>
+          <t xml:space="preserve">result_lose.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E523" t="inlineStr" s="2">
@@ -17198,14 +17198,14 @@
       </c>
       <c r="F523" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦でした。相手にも感謝です</t>
+          <t xml:space="preserve">悔しい…でも、この経験を無駄にしない</t>
         </is>
       </c>
     </row>
     <row r="524" ht="40" customHeight="1">
       <c r="A524" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B524" t="inlineStr" s="2">
@@ -17215,12 +17215,12 @@
       </c>
       <c r="C524" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D524" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">result_win.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E524" t="inlineStr" s="2">
@@ -17230,14 +17230,14 @@
       </c>
       <c r="F524" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…！ みんなのために、絶対に負けたくなかったから…！</t>
+          <t xml:space="preserve">勝てました…！ みんなの頑張りが実った結果です</t>
         </is>
       </c>
     </row>
     <row r="525" ht="40" customHeight="1">
       <c r="A525" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B525" t="inlineStr" s="2">
@@ -17247,12 +17247,12 @@
       </c>
       <c r="C525" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D525" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">result_win.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E525" t="inlineStr" s="2">
@@ -17262,14 +17262,14 @@
       </c>
       <c r="F525" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名前を背負って戦えて…嬉しい。勝ててもっと嬉しい…！</t>
+          <t xml:space="preserve">いい対抗戦でした。相手にも感謝です</t>
         </is>
       </c>
     </row>
     <row r="526" ht="40" customHeight="1">
       <c r="A526" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B526" t="inlineStr" s="2">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="D526" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[3]</t>
+          <t xml:space="preserve">standard.earnest[1]</t>
         </is>
       </c>
       <c r="E526" t="inlineStr" s="2">
@@ -17294,14 +17294,14 @@
       </c>
       <c r="F526" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で戦いました…！ 団体のみんなに恥じない試合ができたなら…</t>
+          <t xml:space="preserve">勝てた…！ みんなのために、絶対に負けたくなかったから…！</t>
         </is>
       </c>
     </row>
     <row r="527" ht="40" customHeight="1">
       <c r="A527" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.earnest[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B527" t="inlineStr" s="2">
@@ -17311,29 +17311,29 @@
       </c>
       <c r="C527" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D527" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.earnest[1]</t>
+          <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
       <c r="E527" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F527" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習してきたことが全部報われた。泣きそう</t>
+          <t xml:space="preserve">団体の名前を背負って戦えて…嬉しい。勝ててもっと嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="528" ht="40" customHeight="1">
       <c r="A528" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.earnest[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.earnest[3]</t>
         </is>
       </c>
       <c r="B528" t="inlineStr" s="2">
@@ -17343,29 +17343,29 @@
       </c>
       <c r="C528" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D528" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.earnest[2]</t>
+          <t xml:space="preserve">standard.earnest[3]</t>
         </is>
       </c>
       <c r="E528" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F528" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの時辞めなくてよかった。この瞬間のために全部あったんだ</t>
+          <t xml:space="preserve">全力で戦いました…！ 団体のみんなに恥じない試合ができたなら…</t>
         </is>
       </c>
     </row>
     <row r="529" ht="40" customHeight="1">
       <c r="A529" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B529" t="inlineStr" s="2">
@@ -17375,29 +17375,29 @@
       </c>
       <c r="C529" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D529" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[1]</t>
+          <t xml:space="preserve">fighter.standard.earnest[1]</t>
         </is>
       </c>
       <c r="E529" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F529" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度チャンスをもらえた。無駄にしません</t>
+          <t xml:space="preserve">練習してきたことが全部報われた。泣きそう</t>
         </is>
       </c>
     </row>
     <row r="530" ht="40" customHeight="1">
       <c r="A530" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.earnest[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.earnest[2]</t>
         </is>
       </c>
       <c r="B530" t="inlineStr" s="2">
@@ -17407,29 +17407,29 @@
       </c>
       <c r="C530" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D530" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.earnest[2]</t>
+          <t xml:space="preserve">fighter.standard.earnest[2]</t>
         </is>
       </c>
       <c r="E530" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F530" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた恩には、積み上げた練習で応えます</t>
+          <t xml:space="preserve">あの時辞めなくてよかった。この瞬間のために全部あったんだ</t>
         </is>
       </c>
     </row>
     <row r="531" ht="40" customHeight="1">
       <c r="A531" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.earnest[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.earnest[1]</t>
         </is>
       </c>
       <c r="B531" t="inlineStr" s="2">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C531" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D531" t="inlineStr" s="12">
@@ -17454,44 +17454,108 @@
       </c>
       <c r="F531" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ていてくれた人がいた。それだけで頑張れます</t>
+          <t xml:space="preserve">もう一度チャンスをもらえた。無駄にしません</t>
         </is>
       </c>
     </row>
     <row r="532" ht="40" customHeight="1">
       <c r="A532" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくれた恩には、積み上げた練習で応えます</t>
+        </is>
+      </c>
+    </row>
+    <row r="533" ht="40" customHeight="1">
+      <c r="A533" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見ていてくれた人がいた。それだけで頑張れます</t>
+        </is>
+      </c>
+    </row>
+    <row r="534" ht="40" customHeight="1">
+      <c r="A534" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.earnest[2]</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr" s="2">
+      <c r="B534" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr" s="12">
+      <c r="D534" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.earnest[2]</t>
         </is>
       </c>
-      <c r="E532" t="inlineStr" s="2">
+      <c r="E534" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F532" t="inlineStr" s="3">
+      <c r="F534" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">期待してもらった分、毎日積み上げていきます</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H532"/>
+  <autoFilter ref="A1:H534"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×真面目.xlsx
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、迷惑をかけるのは分かってます。それでも、あの人とやらせてください。</t>
+          <t xml:space="preserve">社長、迷惑は分かってます。それでも三人で行かせてください。</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">半端な気持ちじゃありません。……あの人と、闘わせてください。</t>
+          <t xml:space="preserve">半端な気持ちじゃありません。……三人で、乗り込ませてください。</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いします。この一戦だけは、逃げたくないんです。</t>
+          <t xml:space="preserve">お願いします。この三連戦だけは、逃げたくないんです。</t>
         </is>
       </c>
     </row>
